--- a/revision_sistematica/riesgo_sesgo/riesgo_sesgo_nataly_trelles.xlsx
+++ b/revision_sistematica/riesgo_sesgo/riesgo_sesgo_nataly_trelles.xlsx
@@ -1880,28 +1880,84 @@
     <comment ref="F27" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
+...rough metagenomic sequencing. Fracture-related infections can be challenging, particularly with concomitant Front. Med. 11:1428432. severe bone defects and multi-resistant microorganisms. We present a case doi: 10.3389/fmed.2024.1428432 of a 42-year-old patient with a fracture-related infection following a war COPYRIGHT injury from a gunshot, resulting in a 12-cm subtrochanteric segmental bone © 2024 Alt, Gessner, Merabishvili, Hitzenbichler, Mannala, Peterhoff, Walter, defect and the det...
+...the detection of four different multi-resistant Gram-negative Pirnay, Hiergeist and Rupp. This is an bacteria. Due to antibiotic drug resistance, treatment with bacteriophages was open-access article distributed under the considered. Phage susceptibility testing revealed the activity of a commercially terms of the Creative Commons Attribution License (CC BY). The use, distribution or available bacteriophage cocktail (Intesti bacteriophage, Eliava Institute, Tbilisi, reproduction in other forums is...
+...ing needs to be obtained (1). 2 Case description Both local and systemic antibiotic therapy are hallmarks of fracture-related infection treatment. However, there are often only limited antibiotic treatment options when multi-drug resistant A 42-year-old man suffered a war injury during the Russian war in bacteria are involved. An alternative or complementary approach for Ukraine. He had a history of a gunshot and a blast injury to his the treatment of complex infections with multi-drug re...</t>
+      </text>
+    </comment>
+    <comment ref="G27" authorId="0" shapeId="0">
+      <text>
+        <t>Del artículo:
+...rough metagenomic sequencing. Fracture-related infections can be challenging, particularly with concomitant Front. Med. 11:1428432. severe bone defects and multi-resistant microorganisms. We present a case doi: 10.3389/fmed.2024.1428432 of a 42-year-old patient with a fracture-related infection following a war COPYRIGHT injury from a gunshot, resulting in a 12-cm subtrochanteric segmental bone © 2024 Alt, Gessner, Merabishvili, Hitzenbichler, Mannala, Peterhoff, Walter, defect and the det...
+...the detection of four different multi-resistant Gram-negative Pirnay, Hiergeist and Rupp. This is an bacteria. Due to antibiotic drug resistance, treatment with bacteriophages was open-access article distributed under the considered. Phage susceptibility testing revealed the activity of a commercially terms of the Creative Commons Attribution License (CC BY). The use, distribution or available bacteriophage cocktail (Intesti bacteriophage, Eliava Institute, Tbilisi, reproduction in other forums is...
+...ing needs to be obtained (1). 2 Case description Both local and systemic antibiotic therapy are hallmarks of fracture-related infection treatment. However, there are often only limited antibiotic treatment options when multi-drug resistant A 42-year-old man suffered a war injury during the Russian war in bacteria are involved. An alternative or complementary approach for Ukraine. He had a history of a gunshot and a blast injury to his the treatment of complex infections with multi-drug re...</t>
+      </text>
+    </comment>
+    <comment ref="H27" authorId="0" shapeId="0">
+      <text>
+        <t>Del artículo:
+...rough metagenomic sequencing. Fracture-related infections can be challenging, particularly with concomitant Front. Med. 11:1428432. severe bone defects and multi-resistant microorganisms. We present a case doi: 10.3389/fmed.2024.1428432 of a 42-year-old patient with a fracture-related infection following a war COPYRIGHT injury from a gunshot, resulting in a 12-cm subtrochanteric segmental bone © 2024 Alt, Gessner, Merabishvili, Hitzenbichler, Mannala, Peterhoff, Walter, defect and the det...
+...the detection of four different multi-resistant Gram-negative Pirnay, Hiergeist and Rupp. This is an bacteria. Due to antibiotic drug resistance, treatment with bacteriophages was open-access article distributed under the considered. Phage susceptibility testing revealed the activity of a commercially terms of the Creative Commons Attribution License (CC BY). The use, distribution or available bacteriophage cocktail (Intesti bacteriophage, Eliava Institute, Tbilisi, reproduction in other forums is...
+...ing needs to be obtained (1). 2 Case description Both local and systemic antibiotic therapy are hallmarks of fracture-related infection treatment. However, there are often only limited antibiotic treatment options when multi-drug resistant A 42-year-old man suffered a war injury during the Russian war in bacteria are involved. An alternative or complementary approach for Ukraine. He had a history of a gunshot and a blast injury to his the treatment of complex infections with multi-drug re...</t>
+      </text>
+    </comment>
+    <comment ref="I27" authorId="0" shapeId="0">
+      <text>
+        <t>Del artículo:
+...rough metagenomic sequencing. Fracture-related infections can be challenging, particularly with concomitant Front. Med. 11:1428432. severe bone defects and multi-resistant microorganisms. We present a case doi: 10.3389/fmed.2024.1428432 of a 42-year-old patient with a fracture-related infection following a war COPYRIGHT injury from a gunshot, resulting in a 12-cm subtrochanteric segmental bone © 2024 Alt, Gessner, Merabishvili, Hitzenbichler, Mannala, Peterhoff, Walter, defect and the det...
+...the detection of four different multi-resistant Gram-negative Pirnay, Hiergeist and Rupp. This is an bacteria. Due to antibiotic drug resistance, treatment with bacteriophages was open-access article distributed under the considered. Phage susceptibility testing revealed the activity of a commercially terms of the Creative Commons Attribution License (CC BY). The use, distribution or available bacteriophage cocktail (Intesti bacteriophage, Eliava Institute, Tbilisi, reproduction in other forums is...
+...ing needs to be obtained (1). 2 Case description Both local and systemic antibiotic therapy are hallmarks of fracture-related infection treatment. However, there are often only limited antibiotic treatment options when multi-drug resistant A 42-year-old man suffered a war injury during the Russian war in bacteria are involved. An alternative or complementary approach for Ukraine. He had a history of a gunshot and a blast injury to his the treatment of complex infections with multi-drug re...</t>
+      </text>
+    </comment>
+    <comment ref="J27" authorId="0" shapeId="0">
+      <text>
+        <t>Del artículo:
+...t and the detection of four different multi-resistant Gram-negative Pirnay, Hiergeist and Rupp. This is an bacteria. Due to antibiotic drug resistance, treatment with bacteriophages was open-access article distributed under the considered. Phage susceptibility testing revealed the activity of a commercially terms of the Creative Commons Attribution License (CC BY). The use, distribution or available bacteriophage cocktail (Intesti bacteriophage, Eliava Institute, Tbilisi, reproduction in other f...
+...commercially terms of the Creative Commons Attribution License (CC BY). The use, distribution or available bacteriophage cocktail (Intesti bacteriophage, Eliava Institute, Tbilisi, reproduction in other forums is permitted, Georgia). This phage cocktail was included in a modified two-stage Masquelet provided the original author(s) and the technique. During the first intervention, the bone was debrided and samples for copyright owner(s) are credited and that the original publication in thi...
+...with these terms. the PMMA spacer was removed and a silver-coated angular stable plate was implanted. The bone defect was filled with a fibular autograft and allograft cancellous bone chips. At the end of the procedure, the Intesti bacteriophage cocktail was injected into a DAC hydrogel and this bacteriophage hydrogel composite was then put onto the angular stable plate. Postoperatively the wound fluid was collected over 72 h, and high-throughput metagenomic sequencing was performed. This...</t>
+      </text>
+    </comment>
+    <comment ref="K27" authorId="0" shapeId="0">
+      <text>
+        <t>Del artículo:
+...rough metagenomic sequencing. Fracture-related infections can be challenging, particularly with concomitant Front. Med. 11:1428432. severe bone defects and multi-resistant microorganisms. We present a case doi: 10.3389/fmed.2024.1428432 of a 42-year-old patient with a fracture-related infection following a war COPYRIGHT injury from a gunshot, resulting in a 12-cm subtrochanteric segmental bone © 2024 Alt, Gessner, Merabishvili, Hitzenbichler, Mannala, Peterhoff, Walter, defect and the det...
+...the detection of four different multi-resistant Gram-negative Pirnay, Hiergeist and Rupp. This is an bacteria. Due to antibiotic drug resistance, treatment with bacteriophages was open-access article distributed under the considered. Phage susceptibility testing revealed the activity of a commercially terms of the Creative Commons Attribution License (CC BY). The use, distribution or available bacteriophage cocktail (Intesti bacteriophage, Eliava Institute, Tbilisi, reproduction in other forums is...
+...ing needs to be obtained (1). 2 Case description Both local and systemic antibiotic therapy are hallmarks of fracture-related infection treatment. However, there are often only limited antibiotic treatment options when multi-drug resistant A 42-year-old man suffered a war injury during the Russian war in bacteria are involved. An alternative or complementary approach for Ukraine. He had a history of a gunshot and a blast injury to his the treatment of complex infections with multi-drug re...</t>
+      </text>
+    </comment>
+    <comment ref="L27" authorId="0" shapeId="0">
+      <text>
+        <t>Del artículo:
+...rough metagenomic sequencing. Fracture-related infections can be challenging, particularly with concomitant Front. Med. 11:1428432. severe bone defects and multi-resistant microorganisms. We present a case doi: 10.3389/fmed.2024.1428432 of a 42-year-old patient with a fracture-related infection following a war COPYRIGHT injury from a gunshot, resulting in a 12-cm subtrochanteric segmental bone © 2024 Alt, Gessner, Merabishvili, Hitzenbichler, Mannala, Peterhoff, Walter, defect and the det...
+...the detection of four different multi-resistant Gram-negative Pirnay, Hiergeist and Rupp. This is an bacteria. Due to antibiotic drug resistance, treatment with bacteriophages was open-access article distributed under the considered. Phage susceptibility testing revealed the activity of a commercially terms of the Creative Commons Attribution License (CC BY). The use, distribution or available bacteriophage cocktail (Intesti bacteriophage, Eliava Institute, Tbilisi, reproduction in other forums is...
+...ing needs to be obtained (1). 2 Case description Both local and systemic antibiotic therapy are hallmarks of fracture-related infection treatment. However, there are often only limited antibiotic treatment options when multi-drug resistant A 42-year-old man suffered a war injury during the Russian war in bacteria are involved. An alternative or complementary approach for Ukraine. He had a history of a gunshot and a blast injury to his the treatment of complex infections with multi-drug re...</t>
+      </text>
+    </comment>
+    <comment ref="F28" authorId="0" shapeId="0">
+      <text>
+        <t>Del artículo:
 ...enassociatedwithhighrisksofmorbidity andmortality.WereporthereacaseofapatientwithanarterialstentandrecurrentPseudomonassep- ticaemiassuccessfullytreatedwithphage–meropenemcombinationtherapy.Methods:A75-year-old femalewitharteriosclerosisandcomorbiditieswentthroughafemoropoplitealbypasswithprosthesis intherightinguinalarea.Afterthebypass,shedevelopedarecurringPseudomonasaeruginosainfec- tionandalsoneutropeniaduringdifferentantibiotics.Arapidlygrowingpseudoaneurysminthe rightinguinalarea...</t>
       </text>
     </comment>
-    <comment ref="G27" authorId="0" shapeId="0">
+    <comment ref="G28" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...enassociatedwithhighrisksofmorbidity andmortality.WereporthereacaseofapatientwithanarterialstentandrecurrentPseudomonassep- ticaemiassuccessfullytreatedwithphage–meropenemcombinationtherapy.Methods:A75-year-old femalewitharteriosclerosisandcomorbiditieswentthroughafemoropoplitealbypasswithprosthesis intherightinguinalarea.Afterthebypass,shedevelopedarecurringPseudomonasaeruginosainfec- tionandalsoneutropeniaduringdifferentantibiotics.Arapidlygrowingpseudoaneurysminthe rightinguinalarea...</t>
       </text>
     </comment>
-    <comment ref="H27" authorId="0" shapeId="0">
+    <comment ref="H28" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...enassociatedwithhighrisksofmorbidity andmortality.WereporthereacaseofapatientwithanarterialstentandrecurrentPseudomonassep- ticaemiassuccessfullytreatedwithphage–meropenemcombinationtherapy.Methods:A75-year-old femalewitharteriosclerosisandcomorbiditieswentthroughafemoropoplitealbypasswithprosthesis intherightinguinalarea.Afterthebypass,shedevelopedarecurringPseudomonasaeruginosainfec- tionandalsoneutropeniaduringdifferentantibiotics.Arapidlygrowingpseudoaneurysminthe rightinguinalarea...</t>
       </text>
     </comment>
-    <comment ref="I27" authorId="0" shapeId="0">
+    <comment ref="I28" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...enassociatedwithhighrisksofmorbidity andmortality.WereporthereacaseofapatientwithanarterialstentandrecurrentPseudomonassep- ticaemiassuccessfullytreatedwithphage–meropenemcombinationtherapy.Methods:A75-year-old femalewitharteriosclerosisandcomorbiditieswentthroughafemoropoplitealbypasswithprosthesis intherightinguinalarea.Afterthebypass,shedevelopedarecurringPseudomonasaeruginosainfec- tionandalsoneutropeniaduringdifferentantibiotics.Arapidlygrowingpseudoaneurysminthe rightinguinalarea...</t>
       </text>
     </comment>
-    <comment ref="J27" authorId="0" shapeId="0">
+    <comment ref="J28" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...ingbloodstreaminfection, latersuspectedtohostaP.aeruginosabiofilm.Removingthestentwasdeemedprecarious,andphage therapywasconsideredasacompassionatetreatmentoption.Athree-phagecocktailinfectingthe P.aeruginosastrainwaspreparedandadministeredintravenouslytogetherwithmeropenemfortwo Citation:Otava,U.E.;Tervo,L.; weeks,afterwhich,aten-monthfollow-upwascarriedout.Results:Noadversereactionsoccurred Havela,R.;Vuotari,L.;Ylänne,M.; duringthephagetherapytreatment,whileinfectionmarkerswerenormali...
@@ -1909,19 +1965,19 @@
 ...found in her bloodstream again. The newly applied arterial prosthesiswasremoved. P.aeruginosaofanotherwisesimilarsusceptibilitypattern,but resistanttolevofloxacin,wasgrowinginthesamplestakenfromtheinguinalareaduring theoperation. Therefore,intravenouspiperacillin–tazobactamwasgiven(4g/0.5gq8hiv) for10days. Tendaysafterthelastdoseoftheantibiotics,thepatienthadahighfever,andP.aerug- inosawasfoundagaininthebloodstream. Cardiacultrasoundwasperformedbutnosigns ofintracardiacinfectionorvegeta...</t>
       </text>
     </comment>
-    <comment ref="K27" authorId="0" shapeId="0">
+    <comment ref="K28" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...enassociatedwithhighrisksofmorbidity andmortality.WereporthereacaseofapatientwithanarterialstentandrecurrentPseudomonassep- ticaemiassuccessfullytreatedwithphage–meropenemcombinationtherapy.Methods:A75-year-old femalewitharteriosclerosisandcomorbiditieswentthroughafemoropoplitealbypasswithprosthesis intherightinguinalarea.Afterthebypass,shedevelopedarecurringPseudomonasaeruginosainfec- tionandalsoneutropeniaduringdifferentantibiotics.Arapidlygrowingpseudoaneurysminthe rightinguinalarea...</t>
       </text>
     </comment>
-    <comment ref="L27" authorId="0" shapeId="0">
+    <comment ref="L28" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...enassociatedwithhighrisksofmorbidity andmortality.WereporthereacaseofapatientwithanarterialstentandrecurrentPseudomonassep- ticaemiassuccessfullytreatedwithphage–meropenemcombinationtherapy.Methods:A75-year-old femalewitharteriosclerosisandcomorbiditieswentthroughafemoropoplitealbypasswithprosthesis intherightinguinalarea.Afterthebypass,shedevelopedarecurringPseudomonasaeruginosainfec- tionandalsoneutropeniaduringdifferentantibiotics.Arapidlygrowingpseudoaneurysminthe rightinguinalarea...</t>
       </text>
     </comment>
-    <comment ref="J28" authorId="0" shapeId="0">
+    <comment ref="J29" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...ion. Cerebralmagneticresonanceimagingshowedmultipleemboliwith Attribution(CCBY)license disseminatedsmallischemicstrokes. ThepatientwastreatedwithaBentallbioprosthetic (https://creativecommons.org/ licenses/by/4.0/). valvereplacementandhigh-doseceftazidimefor6weeks. Viruses2025,17,123 https://doi.org/10.3390/v17010123Viruses2025,17,123 2of6 InMarch2023,hepresentedtothehospitalwithfeverandoxygendependency. Mul- tiplebloodcultureswere,onceagain,positiveforP.aeruginosawiththesameresi...
@@ -1929,7 +1985,7 @@
 ...phage, while an EOP between 0.005 and 0.1 indicates a moderately effectivephageandbetween0and0.005alowefficiencyphage[8]. Thesecondtestwas the broth microdilution assay, which identified the minimum inhibitory concentration (MIC)expressedinplaque-formingunits(PFU)permilliliterofphagetoinhibit80+/−8% of bacterial growth. The EOP values of PP 1450, PP 1777, PP1792 and 1797 were 0.606, 0.932, 0.053 and 0.206, respectively. The MIC of PP 1450, PP 1777, PP1792 and 1797 were1.3×103 PFU/mL,2.0×10...</t>
       </text>
     </comment>
-    <comment ref="F29" authorId="0" shapeId="0">
+    <comment ref="F30" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...sistant infections recently, particularly in people with cystic fibrosis (CF) who are predisposed to infection from Pseudomonas aeruginosa. Case Summary Here, we report the use of phage therapy to treat a chronic P. aeruginosa infection in a 44-year-old woman with CF who underwent bilateral lung transplantation. This individual experienced acute rejection and deteriorating lung function, possibly worsened as a consequence of a P. aeruginosa infection. Phage therapy using phage vB_Pae_10 w...
@@ -1937,7 +1993,7 @@
 ...s lowest (53.1%), while bacterial load in BAL continued increasing (measured by colony-forming units (CFU)/mL using quantitative seeding (8), and a second IV ceftazidime and ciprofloxacin treatment was prescribed. As in vitro antimicrobial susceptibility testing in isolates from CF patients is unreliable (9), the drug regimen was based on tolerability and clinical response. Given the potential implications of the P. aeruginosa infection in exacerbating the graft rejection and the ineffectiveness o...</t>
       </text>
     </comment>
-    <comment ref="G29" authorId="0" shapeId="0">
+    <comment ref="G30" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...sistant infections recently, particularly in people with cystic fibrosis (CF) who are predisposed to infection from Pseudomonas aeruginosa. Case Summary Here, we report the use of phage therapy to treat a chronic P. aeruginosa infection in a 44-year-old woman with CF who underwent bilateral lung transplantation. This individual experienced acute rejection and deteriorating lung function, possibly worsened as a consequence of a P. aeruginosa infection. Phage therapy using phage vB_Pae_10 w...
@@ -1945,7 +2001,7 @@
 ...s lowest (53.1%), while bacterial load in BAL continued increasing (measured by colony-forming units (CFU)/mL using quantitative seeding (8), and a second IV ceftazidime and ciprofloxacin treatment was prescribed. As in vitro antimicrobial susceptibility testing in isolates from CF patients is unreliable (9), the drug regimen was based on tolerability and clinical response. Given the potential implications of the P. aeruginosa infection in exacerbating the graft rejection and the ineffectiveness o...</t>
       </text>
     </comment>
-    <comment ref="H29" authorId="0" shapeId="0">
+    <comment ref="H30" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...sistant infections recently, particularly in people with cystic fibrosis (CF) who are predisposed to infection from Pseudomonas aeruginosa. Case Summary Here, we report the use of phage therapy to treat a chronic P. aeruginosa infection in a 44-year-old woman with CF who underwent bilateral lung transplantation. This individual experienced acute rejection and deteriorating lung function, possibly worsened as a consequence of a P. aeruginosa infection. Phage therapy using phage vB_Pae_10 w...
@@ -1953,7 +2009,7 @@
 ...s lowest (53.1%), while bacterial load in BAL continued increasing (measured by colony-forming units (CFU)/mL using quantitative seeding (8), and a second IV ceftazidime and ciprofloxacin treatment was prescribed. As in vitro antimicrobial susceptibility testing in isolates from CF patients is unreliable (9), the drug regimen was based on tolerability and clinical response. Given the potential implications of the P. aeruginosa infection in exacerbating the graft rejection and the ineffectiveness o...</t>
       </text>
     </comment>
-    <comment ref="I29" authorId="0" shapeId="0">
+    <comment ref="I30" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...sistant infections recently, particularly in people with cystic fibrosis (CF) who are predisposed to infection from Pseudomonas aeruginosa. Case Summary Here, we report the use of phage therapy to treat a chronic P. aeruginosa infection in a 44-year-old woman with CF who underwent bilateral lung transplantation. This individual experienced acute rejection and deteriorating lung function, possibly worsened as a consequence of a P. aeruginosa infection. Phage therapy using phage vB_Pae_10 w...
@@ -1961,7 +2017,7 @@
 ...s lowest (53.1%), while bacterial load in BAL continued increasing (measured by colony-forming units (CFU)/mL using quantitative seeding (8), and a second IV ceftazidime and ciprofloxacin treatment was prescribed. As in vitro antimicrobial susceptibility testing in isolates from CF patients is unreliable (9), the drug regimen was based on tolerability and clinical response. Given the potential implications of the P. aeruginosa infection in exacerbating the graft rejection and the ineffectiveness o...</t>
       </text>
     </comment>
-    <comment ref="J29" authorId="0" shapeId="0">
+    <comment ref="J30" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...nderwent bilateral lung transplantation. This individual experienced acute rejection and deteriorating lung function, possibly worsened as a consequence of a P. aeruginosa infection. Phage therapy using phage vB_Pae_10 was administered via nebulizer alongside standard antimicrobials in two 10-day courses. Clinical and microbiological assessments indicated an initial reduction in bacterial load along with an improvement in lung function. Phage therapy was well-tolerated with no adver...
@@ -1969,7 +2025,7 @@
 ...lular rejection grade A2B2, which required additional immunosuppressive treatments (Table 1). By the end of August, %FEV1/FVC declined to 57.8%, and P. aeruginosa was isolated from a bronchoalveolar lavage (BAL) sample, prompting the first intravenous (IV) ceftazidime and ciprofloxacin treatment. The persistent rejection worsened her lung function and overall condition, and in October, she received multiple ineffective IV antibiotic cycles for the P. aeruginosa infection (Table 1), susp...</t>
       </text>
     </comment>
-    <comment ref="K29" authorId="0" shapeId="0">
+    <comment ref="K30" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...sistant infections recently, particularly in people with cystic fibrosis (CF) who are predisposed to infection from Pseudomonas aeruginosa. Case Summary Here, we report the use of phage therapy to treat a chronic P. aeruginosa infection in a 44-year-old woman with CF who underwent bilateral lung transplantation. This individual experienced acute rejection and deteriorating lung function, possibly worsened as a consequence of a P. aeruginosa infection. Phage therapy using phage vB_Pae_10 w...
@@ -1977,7 +2033,7 @@
 ...s lowest (53.1%), while bacterial load in BAL continued increasing (measured by colony-forming units (CFU)/mL using quantitative seeding (8), and a second IV ceftazidime and ciprofloxacin treatment was prescribed. As in vitro antimicrobial susceptibility testing in isolates from CF patients is unreliable (9), the drug regimen was based on tolerability and clinical response. Given the potential implications of the P. aeruginosa infection in exacerbating the graft rejection and the ineffectiveness o...</t>
       </text>
     </comment>
-    <comment ref="L29" authorId="0" shapeId="0">
+    <comment ref="L30" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...sistant infections recently, particularly in people with cystic fibrosis (CF) who are predisposed to infection from Pseudomonas aeruginosa. Case Summary Here, we report the use of phage therapy to treat a chronic P. aeruginosa infection in a 44-year-old woman with CF who underwent bilateral lung transplantation. This individual experienced acute rejection and deteriorating lung function, possibly worsened as a consequence of a P. aeruginosa infection. Phage therapy using phage vB_Pae_10 w...
@@ -1985,7 +2041,7 @@
 ...s lowest (53.1%), while bacterial load in BAL continued increasing (measured by colony-forming units (CFU)/mL using quantitative seeding (8), and a second IV ceftazidime and ciprofloxacin treatment was prescribed. As in vitro antimicrobial susceptibility testing in isolates from CF patients is unreliable (9), the drug regimen was based on tolerability and clinical response. Given the potential implications of the P. aeruginosa infection in exacerbating the graft rejection and the ineffectiveness o...</t>
       </text>
     </comment>
-    <comment ref="J30" authorId="0" shapeId="0">
+    <comment ref="J31" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...ionsto furthercharacterizewhatdeterminestherapeuticsuccessorfailure.Inthis work,wereportthestoryofatoddlerwhosufferedfromextensivelydrug- resistantPseudomonasaeruginosasepsisafterlivertransplantation.Hewas treatedbyabacteriophage-antibioticintravenouscombinationtherapyfor 86days.Thissalvagetherapywaswelltolerated,withoutantibody-mediated phageneutralization.Itwasassociatedwithobjectiveclinicalandmicro- biologicalimprovement,eventuallyallowingforliverretransplantationand completeresoluti...
@@ -1993,31 +2049,31 @@
 ...aining one thetoddlerpresentedintrahepaticbiliarystrictures,multiplehepatic Staphylococcusaureusphage(ISP)andtwoP.aeruginosaphages(PNM abscesses, cholangitis, and severe septicemia caused by XDR and 14-1)8. Before clinical application, the phage preparation was Fig.1|Clinicaltimeline.Timelineofthemostrelevantsurgicalprocedures post-LDLT,heenteredaseveresepticemiaduetoXDRPseudomonasaerugi- (lightgreen),microbiologicalresults(lightblue),antibiotictherapies(dark nosa.ABOcABOcompatible,ABOiABOinc...</t>
       </text>
     </comment>
-    <comment ref="F31" authorId="0" shapeId="0">
+    <comment ref="F32" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...n- producing P. aeruginosa strain and the timeline of the dsRNA phage therapy. (A) The P. aeruginosa strain PA- LX01 from the patient produces the brown pyomelanin, and phiYY lyses this strain efficiently. (B) The results of the antibiotic susceptibility testing for P. aeruginosa strains isolated before and after phage therapy. (C) Growth curve of PA- LX01 strain in the presence or absence of phiYY. Each assay was repeated three times. (D) The timeline for the three courses of dsRNA phage therapy,...</t>
       </text>
     </comment>
-    <comment ref="G31" authorId="0" shapeId="0">
+    <comment ref="G32" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...n- producing P. aeruginosa strain and the timeline of the dsRNA phage therapy. (A) The P. aeruginosa strain PA- LX01 from the patient produces the brown pyomelanin, and phiYY lyses this strain efficiently. (B) The results of the antibiotic susceptibility testing for P. aeruginosa strains isolated before and after phage therapy. (C) Growth curve of PA- LX01 strain in the presence or absence of phiYY. Each assay was repeated three times. (D) The timeline for the three courses of dsRNA phage therapy,...</t>
       </text>
     </comment>
-    <comment ref="H31" authorId="0" shapeId="0">
+    <comment ref="H32" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...n- producing P. aeruginosa strain and the timeline of the dsRNA phage therapy. (A) The P. aeruginosa strain PA- LX01 from the patient produces the brown pyomelanin, and phiYY lyses this strain efficiently. (B) The results of the antibiotic susceptibility testing for P. aeruginosa strains isolated before and after phage therapy. (C) Growth curve of PA- LX01 strain in the presence or absence of phiYY. Each assay was repeated three times. (D) The timeline for the three courses of dsRNA phage therapy,...</t>
       </text>
     </comment>
-    <comment ref="I31" authorId="0" shapeId="0">
+    <comment ref="I32" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...n- producing P. aeruginosa strain and the timeline of the dsRNA phage therapy. (A) The P. aeruginosa strain PA- LX01 from the patient produces the brown pyomelanin, and phiYY lyses this strain efficiently. (B) The results of the antibiotic susceptibility testing for P. aeruginosa strains isolated before and after phage therapy. (C) Growth curve of PA- LX01 strain in the presence or absence of phiYY. Each assay was repeated three times. (D) The timeline for the three courses of dsRNA phage therapy,...</t>
       </text>
     </comment>
-    <comment ref="J31" authorId="0" shapeId="0">
+    <comment ref="J32" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...l lung disease (ILD) and chronic lung infec- Tongyu Zhu and Nannan Wu, Shanghai tion. Phage therapy was used as a last resort for this patient. The three- Public Health Clinical Center, Shanghai Institute of Phage, Fudan University, course nebulized phiYY treatment was used to reduce the bacterial burden Shanghai 201508, China and clinical symptoms of the patient. Recurrences of P. aeruginosa infections Email: tyzhu@fudan.edu.cn and were observed 1– 3 days post phage therapy. The re...
@@ -2025,19 +2081,19 @@
 ...due to airway dam- of Zhongshan Hospital of Fudan University, Shanghai, age, the loss of lung function in CF patients and the China. Phage phiYY was diluted in saline to 10 ml and formation of biofilms. administered via the vibrating- mesh nebulizer. EXPERIMENTAL PROCEDURES Determination of phage sensitivity on clinical strains Ethics approval statement The susceptibilities of the target bacteria to phages This study has been approved by the Ethics Committee were measured by the eff...</t>
       </text>
     </comment>
-    <comment ref="K31" authorId="0" shapeId="0">
+    <comment ref="K32" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...n- producing P. aeruginosa strain and the timeline of the dsRNA phage therapy. (A) The P. aeruginosa strain PA- LX01 from the patient produces the brown pyomelanin, and phiYY lyses this strain efficiently. (B) The results of the antibiotic susceptibility testing for P. aeruginosa strains isolated before and after phage therapy. (C) Growth curve of PA- LX01 strain in the presence or absence of phiYY. Each assay was repeated three times. (D) The timeline for the three courses of dsRNA phage therapy,...</t>
       </text>
     </comment>
-    <comment ref="L31" authorId="0" shapeId="0">
+    <comment ref="L32" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...n- producing P. aeruginosa strain and the timeline of the dsRNA phage therapy. (A) The P. aeruginosa strain PA- LX01 from the patient produces the brown pyomelanin, and phiYY lyses this strain efficiently. (B) The results of the antibiotic susceptibility testing for P. aeruginosa strains isolated before and after phage therapy. (C) Growth curve of PA- LX01 strain in the presence or absence of phiYY. Each assay was repeated three times. (D) The timeline for the three courses of dsRNA phage therapy,...</t>
       </text>
     </comment>
-    <comment ref="F32" authorId="0" shapeId="0">
+    <comment ref="F33" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...e necrotizing EDITEDBY RiteshSevalkar, UniversityofAlabamaatBirmingham, fasciitis caused by Panton- UnitedStates REVIEWEDBY JenniferNWalker, Valentine leukocidin-producing UniversityofTexasHealthScienceCenterat Houston,UnitedStates MRSA in a 12-year-old boy ArturJSabat, UniversityMedicalCenterGroningen, Netherlands *CORRESPONDENCE Brieuc Van Nieuwenhuyse1*†, Mathilde Balcaen2†, Olga Chatzis3, BrieucVanNieuwenhuyse Astrid Haenecour2, Emilien Derycke2, Thierry Detaille2, brieuc.vannieuwenhu...
@@ -2045,7 +2101,7 @@
 ...sstatewassignificantlydeterioratingtoa life-threatening situation, despite maximal SOC management. Case description Necrotizing fasciitis diagnosis was assessed based on magnetic resonance imaging (MRI) findings (Figure 2), microbiological A 12-year-old boy with no significant medical or surgical culture findings (S. aureus-positive pus and blood cultures), and history was transferred (D0) to the Pediatric Intensive Care Unit aforementioned evidence of compartment syndrome by multiple (PI...</t>
       </text>
     </comment>
-    <comment ref="G32" authorId="0" shapeId="0">
+    <comment ref="G33" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...e necrotizing EDITEDBY RiteshSevalkar, UniversityofAlabamaatBirmingham, fasciitis caused by Panton- UnitedStates REVIEWEDBY JenniferNWalker, Valentine leukocidin-producing UniversityofTexasHealthScienceCenterat Houston,UnitedStates MRSA in a 12-year-old boy ArturJSabat, UniversityMedicalCenterGroningen, Netherlands *CORRESPONDENCE Brieuc Van Nieuwenhuyse1*†, Mathilde Balcaen2†, Olga Chatzis3, BrieucVanNieuwenhuyse Astrid Haenecour2, Emilien Derycke2, Thierry Detaille2, brieuc.vannieuwenhu...
@@ -2053,7 +2109,7 @@
 ...sstatewassignificantlydeterioratingtoa life-threatening situation, despite maximal SOC management. Case description Necrotizing fasciitis diagnosis was assessed based on magnetic resonance imaging (MRI) findings (Figure 2), microbiological A 12-year-old boy with no significant medical or surgical culture findings (S. aureus-positive pus and blood cultures), and history was transferred (D0) to the Pediatric Intensive Care Unit aforementioned evidence of compartment syndrome by multiple (PI...</t>
       </text>
     </comment>
-    <comment ref="H32" authorId="0" shapeId="0">
+    <comment ref="H33" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...e necrotizing EDITEDBY RiteshSevalkar, UniversityofAlabamaatBirmingham, fasciitis caused by Panton- UnitedStates REVIEWEDBY JenniferNWalker, Valentine leukocidin-producing UniversityofTexasHealthScienceCenterat Houston,UnitedStates MRSA in a 12-year-old boy ArturJSabat, UniversityMedicalCenterGroningen, Netherlands *CORRESPONDENCE Brieuc Van Nieuwenhuyse1*†, Mathilde Balcaen2†, Olga Chatzis3, BrieucVanNieuwenhuyse Astrid Haenecour2, Emilien Derycke2, Thierry Detaille2, brieuc.vannieuwenhu...
@@ -2061,7 +2117,7 @@
 ...sstatewassignificantlydeterioratingtoa life-threatening situation, despite maximal SOC management. Case description Necrotizing fasciitis diagnosis was assessed based on magnetic resonance imaging (MRI) findings (Figure 2), microbiological A 12-year-old boy with no significant medical or surgical culture findings (S. aureus-positive pus and blood cultures), and history was transferred (D0) to the Pediatric Intensive Care Unit aforementioned evidence of compartment syndrome by multiple (PI...</t>
       </text>
     </comment>
-    <comment ref="I32" authorId="0" shapeId="0">
+    <comment ref="I33" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...e necrotizing EDITEDBY RiteshSevalkar, UniversityofAlabamaatBirmingham, fasciitis caused by Panton- UnitedStates REVIEWEDBY JenniferNWalker, Valentine leukocidin-producing UniversityofTexasHealthScienceCenterat Houston,UnitedStates MRSA in a 12-year-old boy ArturJSabat, UniversityMedicalCenterGroningen, Netherlands *CORRESPONDENCE Brieuc Van Nieuwenhuyse1*†, Mathilde Balcaen2†, Olga Chatzis3, BrieucVanNieuwenhuyse Astrid Haenecour2, Emilien Derycke2, Thierry Detaille2, brieuc.vannieuwenhu...
@@ -2069,7 +2125,7 @@
 ...sstatewassignificantlydeterioratingtoa life-threatening situation, despite maximal SOC management. Case description Necrotizing fasciitis diagnosis was assessed based on magnetic resonance imaging (MRI) findings (Figure 2), microbiological A 12-year-old boy with no significant medical or surgical culture findings (S. aureus-positive pus and blood cultures), and history was transferred (D0) to the Pediatric Intensive Care Unit aforementioned evidence of compartment syndrome by multiple (PI...</t>
       </text>
     </comment>
-    <comment ref="J32" authorId="0" shapeId="0">
+    <comment ref="J33" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...ic failure as well as Hospital ([QAMH], Brussels, Belgium) after on-plate phage liver,kidneyandmuscledamage,leadingtoPICUadmission.Blood susceptibility testing (“phagogram”) revealed that phage ISP had cultures were performed and empirical intravenous (IV) potentlyticpoweragainstthepatient’sMRSA-PVLstrain(EOP=1, flucloxacillin, clindamycin and cefotaxime were initiated. i.e.“efficiencyofplating”,aphage’srelativelyticefficiencyonaclinical Exceedingintramuscularpressurewasmeasuredinalleig...
@@ -2077,7 +2133,7 @@
 ...its(PFU)/mL, was Vasopressor therapy, sedation and endotracheal intubation diluted100timesinNaCl0,9%toreachatherapeutictiterof107PFU/ were maintained upon return to PICU. Microbiological cultures mL.Multi-routePTwastheninitiatedusingthis107PFU/mLsolution of pus and blood grew for methicillin-resistant Staphylococcus (Figure1).IVPTwasadministeredat50mLover6hevery24hduring aureus (MRSA) producing Panton-Valentine Leukocidin (PVL). 22 days (D+9 to D+30). Intra-pleural and intra-per...</t>
       </text>
     </comment>
-    <comment ref="K32" authorId="0" shapeId="0">
+    <comment ref="K33" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...e necrotizing EDITEDBY RiteshSevalkar, UniversityofAlabamaatBirmingham, fasciitis caused by Panton- UnitedStates REVIEWEDBY JenniferNWalker, Valentine leukocidin-producing UniversityofTexasHealthScienceCenterat Houston,UnitedStates MRSA in a 12-year-old boy ArturJSabat, UniversityMedicalCenterGroningen, Netherlands *CORRESPONDENCE Brieuc Van Nieuwenhuyse1*†, Mathilde Balcaen2†, Olga Chatzis3, BrieucVanNieuwenhuyse Astrid Haenecour2, Emilien Derycke2, Thierry Detaille2, brieuc.vannieuwenhu...
@@ -2085,7 +2141,7 @@
 ...sstatewassignificantlydeterioratingtoa life-threatening situation, despite maximal SOC management. Case description Necrotizing fasciitis diagnosis was assessed based on magnetic resonance imaging (MRI) findings (Figure 2), microbiological A 12-year-old boy with no significant medical or surgical culture findings (S. aureus-positive pus and blood cultures), and history was transferred (D0) to the Pediatric Intensive Care Unit aforementioned evidence of compartment syndrome by multiple (PI...</t>
       </text>
     </comment>
-    <comment ref="L32" authorId="0" shapeId="0">
+    <comment ref="L33" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...e necrotizing EDITEDBY RiteshSevalkar, UniversityofAlabamaatBirmingham, fasciitis caused by Panton- UnitedStates REVIEWEDBY JenniferNWalker, Valentine leukocidin-producing UniversityofTexasHealthScienceCenterat Houston,UnitedStates MRSA in a 12-year-old boy ArturJSabat, UniversityMedicalCenterGroningen, Netherlands *CORRESPONDENCE Brieuc Van Nieuwenhuyse1*†, Mathilde Balcaen2†, Olga Chatzis3, BrieucVanNieuwenhuyse Astrid Haenecour2, Emilien Derycke2, Thierry Detaille2, brieuc.vannieuwenhu...
@@ -2093,7 +2149,7 @@
 ...sstatewassignificantlydeterioratingtoa life-threatening situation, despite maximal SOC management. Case description Necrotizing fasciitis diagnosis was assessed based on magnetic resonance imaging (MRI) findings (Figure 2), microbiological A 12-year-old boy with no significant medical or surgical culture findings (S. aureus-positive pus and blood cultures), and history was transferred (D0) to the Pediatric Intensive Care Unit aforementioned evidence of compartment syndrome by multiple (PI...</t>
       </text>
     </comment>
-    <comment ref="J33" authorId="0" shapeId="0">
+    <comment ref="J34" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...calcourseofpatientwithrefractoryPseudomonasaeruginosa computedtomography,MDTmulti-disciplinaryteam,PICCPeripherallyInserted vasculargraftinfection.ThepatientexperiencedrecurrentPseudomonasaeru- CentralCatheter,Post-PTPost-phagetherapy,IVPTZintravenousPiperacillin/ ginosabacteremiadespiteappropriateculture-directedantibiotictherapy.Ther- Tazobactam,PET-CTPositronEmissionTomography(PET)andComputedTomo- apeuticdrugmonitoring(TDM)indicatedthatstandarddosingachieved graphy(CT);aFluoroquinolo...
@@ -2101,31 +2157,31 @@
 ...kentodeterminephagepresenceinpatientblood(day0,8and15). nisteredfortwoweeksinlateSeptember2024totargetthesuspectedbiofilm- X,therapeuticdrugmonitoring(TDM)showedinadequatesub-therapeuticcon- associatedcomponentoftheinfection.Duringprolongedintravenousantibiotic centrationofantibiotics.✓,Therapeuticdrugmonitoringshowedadequatether- therapy,recurrentPICCline–relatedexitsiteinfectionsoccurred.Givensustained apeuticconcentrationofantibiotics;X*,Thedoseoflevofloxacinwasreducedto clinicalandr...</t>
       </text>
     </comment>
-    <comment ref="F34" authorId="0" shapeId="0">
+    <comment ref="F35" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...an attempt to avoid catas- tionkineticsandtreatmentresponsetoadjunctivephagetherapyin trophic outcomes from extensive chronic Pseudomonas aeruginosa adult patients with overwhelming Staphylococcus aureus bacter- osteoarticular infection in a 7-year-old child. Monitoring of phage aemiaandsepticshock(PetrovicFabijanet al,2020)butuncertain- andbacterialkineticsallowedreal-timephagedoseadjustment,and ties remain about optimal dosing and treatment duration. Here we alongwithmarkersofthehumanh...</t>
       </text>
     </comment>
-    <comment ref="G34" authorId="0" shapeId="0">
+    <comment ref="G35" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...an attempt to avoid catas- tionkineticsandtreatmentresponsetoadjunctivephagetherapyin trophic outcomes from extensive chronic Pseudomonas aeruginosa adult patients with overwhelming Staphylococcus aureus bacter- osteoarticular infection in a 7-year-old child. Monitoring of phage aemiaandsepticshock(PetrovicFabijanet al,2020)butuncertain- andbacterialkineticsallowedreal-timephagedoseadjustment,and ties remain about optimal dosing and treatment duration. Here we alongwithmarkersofthehumanh...</t>
       </text>
     </comment>
-    <comment ref="H34" authorId="0" shapeId="0">
+    <comment ref="H35" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...an attempt to avoid catas- tionkineticsandtreatmentresponsetoadjunctivephagetherapyin trophic outcomes from extensive chronic Pseudomonas aeruginosa adult patients with overwhelming Staphylococcus aureus bacter- osteoarticular infection in a 7-year-old child. Monitoring of phage aemiaandsepticshock(PetrovicFabijanet al,2020)butuncertain- andbacterialkineticsallowedreal-timephagedoseadjustment,and ties remain about optimal dosing and treatment duration. Here we alongwithmarkersofthehumanh...</t>
       </text>
     </comment>
-    <comment ref="I34" authorId="0" shapeId="0">
+    <comment ref="I35" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...an attempt to avoid catas- tionkineticsandtreatmentresponsetoadjunctivephagetherapyin trophic outcomes from extensive chronic Pseudomonas aeruginosa adult patients with overwhelming Staphylococcus aureus bacter- osteoarticular infection in a 7-year-old child. Monitoring of phage aemiaandsepticshock(PetrovicFabijanet al,2020)butuncertain- andbacterialkineticsallowedreal-timephagedoseadjustment,and ties remain about optimal dosing and treatment duration. Here we alongwithmarkersofthehumanh...</t>
       </text>
     </comment>
-    <comment ref="J34" authorId="0" shapeId="0">
+    <comment ref="J35" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...uginosa adult patients with overwhelming Staphylococcus aureus bacter- osteoarticular infection in a 7-year-old child. Monitoring of phage aemiaandsepticshock(PetrovicFabijanet al,2020)butuncertain- andbacterialkineticsallowedreal-timephagedoseadjustment,and ties remain about optimal dosing and treatment duration. Here we alongwithmarkersofthehumanhostresponse,indicatedasignifi- describe phage, bacterial and host responses to intravenous (IV) cant therapeutic effect within two we...
@@ -2133,19 +2189,19 @@
 ...domonas aeruginosa (Ppa2.1; efficiency of plating [EOP] 1) was unaffectedbytheseantibioticsin vitro(additiveinteraction). Bacteriophages (phages), first used as antibacterial agents more Transiently increased heel pain 8 h after the first dose of thanacenturyago(Abedonet al,2011),offernewhopeforhighly PASA16wasfollowedbyfeverto39.7°Cseveralhourslater(Fig 2). 1 DepartmentofInfectiousDiseasesandMicrobiology,TheChildren’sHospitalatWestmead,Westmead,NSW,Australia 2 SydneyMedicalScho...</t>
       </text>
     </comment>
-    <comment ref="K34" authorId="0" shapeId="0">
+    <comment ref="K35" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...an attempt to avoid catas- tionkineticsandtreatmentresponsetoadjunctivephagetherapyin trophic outcomes from extensive chronic Pseudomonas aeruginosa adult patients with overwhelming Staphylococcus aureus bacter- osteoarticular infection in a 7-year-old child. Monitoring of phage aemiaandsepticshock(PetrovicFabijanet al,2020)butuncertain- andbacterialkineticsallowedreal-timephagedoseadjustment,and ties remain about optimal dosing and treatment duration. Here we alongwithmarkersofthehumanh...</t>
       </text>
     </comment>
-    <comment ref="L34" authorId="0" shapeId="0">
+    <comment ref="L35" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...an attempt to avoid catas- tionkineticsandtreatmentresponsetoadjunctivephagetherapyin trophic outcomes from extensive chronic Pseudomonas aeruginosa adult patients with overwhelming Staphylococcus aureus bacter- osteoarticular infection in a 7-year-old child. Monitoring of phage aemiaandsepticshock(PetrovicFabijanet al,2020)butuncertain- andbacterialkineticsallowedreal-timephagedoseadjustment,and ties remain about optimal dosing and treatment duration. Here we alongwithmarkersofthehumanh...</t>
       </text>
     </comment>
-    <comment ref="J35" authorId="0" shapeId="0">
+    <comment ref="J36" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...redtoremovethecementandtode- 1 bride an abscess located in the psoas muscle. Negative-pressure No phage 0.9 woundtherapywasimplementedbyusingavacuum-assistedclo- 1450 suresystem(VACVR Therapy,KCI,USA).MSSAgrewincultureandthe patientreceivedintravenouscefazolin,replacedbyimipenem/cilas- 0.8 1777 tatin as he developed a catheter-related bacteraemia due to 1792 ceftazidime-resistant Pseudomonas aeruginosa. Despite the 0.7 therapy,thepatientstillhadfeverwithpurulentlocalsecretionwith- 1797...
@@ -2153,35 +2209,35 @@
 ...–4 8×10–5 0.4 0.3 0.2 0.1 0 0 1 2 3 4 5 6 7 8 9 10 11 12 Time (h) Figure1. Tenanti-P.aeruginosanaturalstrictlylyticphagesweretested [efficiency of plating(EOP) analysis and growthinhibitionin liquid cul- ture].TheEOPscoreisdefinedbythephagetitreonthepatient’sstrain dividedbythephagetitreonareferencestrainshowingthemaximum titreobserved.8Thecloserthescoreisto1,themoreeffectivethephage is,indicatingthatitwillbeactiveatlowconcentration.Forthemeasure- mentofgrowthinhibitioninliquidmed...</t>
       </text>
     </comment>
-    <comment ref="F36" authorId="0" shapeId="0">
+    <comment ref="F37" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...t excision and secondary bioticsandphagetherapyhasbeenadrivingforceforcontinued revascularization [8]. However, many patients presenting with researchintothepotentialclinicalutilityofphagetherapy. vascular graft infections have significant comorbidities and are However,oneobviousdrawbacktophagetherapyistheclear oftencriticallyill,complicatingsurgicalinterventionandreducing evidencethatbacteriacanreadilyevolveresistancetophagein- likelihood of a positive clinical outcome. Despite best m...
 ...heunderstand- ingofevolutionarybiologyisvitaltothedevelopmentandadmin- DISCUSSION istration of phage therapy in humans. Schooley et al. reported Theargumentforuseofphagetherapyinbiofilm-associatedin- the personalized phage-based therapy in a 68-year-old diabetic fectionsisoldandhasastoriedpast.However,phageabilityto patient with necrotizing pancreatitis complicated by a MDR disrupt biofilms where traditional antibioticsfail isa significant A.baumaniiinfection[19].Ninedifferentphageswithly...</t>
       </text>
     </comment>
-    <comment ref="G36" authorId="0" shapeId="0">
+    <comment ref="G37" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...t excision and secondary bioticsandphagetherapyhasbeenadrivingforceforcontinued revascularization [8]. However, many patients presenting with researchintothepotentialclinicalutilityofphagetherapy. vascular graft infections have significant comorbidities and are However,oneobviousdrawbacktophagetherapyistheclear oftencriticallyill,complicatingsurgicalinterventionandreducing evidencethatbacteriacanreadilyevolveresistancetophagein- likelihood of a positive clinical outcome. Despite best m...
 ...heunderstand- ingofevolutionarybiologyisvitaltothedevelopmentandadmin- DISCUSSION istration of phage therapy in humans. Schooley et al. reported Theargumentforuseofphagetherapyinbiofilm-associatedin- the personalized phage-based therapy in a 68-year-old diabetic fectionsisoldandhasastoriedpast.However,phageabilityto patient with necrotizing pancreatitis complicated by a MDR disrupt biofilms where traditional antibioticsfail isa significant A.baumaniiinfection[19].Ninedifferentphageswithly...</t>
       </text>
     </comment>
-    <comment ref="H36" authorId="0" shapeId="0">
+    <comment ref="H37" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...t excision and secondary bioticsandphagetherapyhasbeenadrivingforceforcontinued revascularization [8]. However, many patients presenting with researchintothepotentialclinicalutilityofphagetherapy. vascular graft infections have significant comorbidities and are However,oneobviousdrawbacktophagetherapyistheclear oftencriticallyill,complicatingsurgicalinterventionandreducing evidencethatbacteriacanreadilyevolveresistancetophagein- likelihood of a positive clinical outcome. Despite best m...
 ...heunderstand- ingofevolutionarybiologyisvitaltothedevelopmentandadmin- DISCUSSION istration of phage therapy in humans. Schooley et al. reported Theargumentforuseofphagetherapyinbiofilm-associatedin- the personalized phage-based therapy in a 68-year-old diabetic fectionsisoldandhasastoriedpast.However,phageabilityto patient with necrotizing pancreatitis complicated by a MDR disrupt biofilms where traditional antibioticsfail isa significant A.baumaniiinfection[19].Ninedifferentphageswithly...</t>
       </text>
     </comment>
-    <comment ref="I36" authorId="0" shapeId="0">
+    <comment ref="I37" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...t excision and secondary bioticsandphagetherapyhasbeenadrivingforceforcontinued revascularization [8]. However, many patients presenting with researchintothepotentialclinicalutilityofphagetherapy. vascular graft infections have significant comorbidities and are However,oneobviousdrawbacktophagetherapyistheclear oftencriticallyill,complicatingsurgicalinterventionandreducing evidencethatbacteriacanreadilyevolveresistancetophagein- likelihood of a positive clinical outcome. Despite best m...
 ...heunderstand- ingofevolutionarybiologyisvitaltothedevelopmentandadmin- DISCUSSION istration of phage therapy in humans. Schooley et al. reported Theargumentforuseofphagetherapyinbiofilm-associatedin- the personalized phage-based therapy in a 68-year-old diabetic fectionsisoldandhasastoriedpast.However,phageabilityto patient with necrotizing pancreatitis complicated by a MDR disrupt biofilms where traditional antibioticsfail isa significant A.baumaniiinfection[19].Ninedifferentphageswithly...</t>
       </text>
     </comment>
-    <comment ref="J36" authorId="0" shapeId="0">
+    <comment ref="J37" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...their co-administered treatment would not adversely affect bio- cationofphageOMKO1,weperformedinvitrobiofilmreduction filmreductioninthepatient. assays using the strain isolated from fistular discharge of the We then determined the minimum dose of phage OMKO1 patient. requiredtoremovebiofilmsintheabsenceofantibiotictoprovide Biofilmsweregrownon3mm(cid:2)3mmsectionsofDacronby guidancefortheinvivoefficacy,undertheconservativeassump- inoculatingeachsectionin150ml0.1(cid:2)LBbrothina...
@@ -2189,45 +2245,45 @@
 ...iofilmreductionassays.Assay bilateralpectoralismajorflaps.Thepatientwasadmittedagainin treatmentsconsistedofserial10-folddilutionsofphageOMKO1 early 2013 for recurrent P. aeruginosa infection (confirmed by startingat10e10plaqueformingunits(PFU)perml.Celldensities blood and deep wound culture) and a new mediastinal fistula (OD )werethenusedtoestimatetheminimummultiplicityof which drained purulent material. The patient was deemed too 600 infection(MOI:phageparticlespercell)require...</t>
       </text>
     </comment>
-    <comment ref="K36" authorId="0" shapeId="0">
+    <comment ref="K37" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...t excision and secondary bioticsandphagetherapyhasbeenadrivingforceforcontinued revascularization [8]. However, many patients presenting with researchintothepotentialclinicalutilityofphagetherapy. vascular graft infections have significant comorbidities and are However,oneobviousdrawbacktophagetherapyistheclear oftencriticallyill,complicatingsurgicalinterventionandreducing evidencethatbacteriacanreadilyevolveresistancetophagein- likelihood of a positive clinical outcome. Despite best m...
 ...heunderstand- ingofevolutionarybiologyisvitaltothedevelopmentandadmin- DISCUSSION istration of phage therapy in humans. Schooley et al. reported Theargumentforuseofphagetherapyinbiofilm-associatedin- the personalized phage-based therapy in a 68-year-old diabetic fectionsisoldandhasastoriedpast.However,phageabilityto patient with necrotizing pancreatitis complicated by a MDR disrupt biofilms where traditional antibioticsfail isa significant A.baumaniiinfection[19].Ninedifferentphageswithly...</t>
       </text>
     </comment>
-    <comment ref="L36" authorId="0" shapeId="0">
+    <comment ref="L37" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...t excision and secondary bioticsandphagetherapyhasbeenadrivingforceforcontinued revascularization [8]. However, many patients presenting with researchintothepotentialclinicalutilityofphagetherapy. vascular graft infections have significant comorbidities and are However,oneobviousdrawbacktophagetherapyistheclear oftencriticallyill,complicatingsurgicalinterventionandreducing evidencethatbacteriacanreadilyevolveresistancetophagein- likelihood of a positive clinical outcome. Despite best m...
 ...heunderstand- ingofevolutionarybiologyisvitaltothedevelopmentandadmin- DISCUSSION istration of phage therapy in humans. Schooley et al. reported Theargumentforuseofphagetherapyinbiofilm-associatedin- the personalized phage-based therapy in a 68-year-old diabetic fectionsisoldandhasastoriedpast.However,phageabilityto patient with necrotizing pancreatitis complicated by a MDR disrupt biofilms where traditional antibioticsfail isa significant A.baumaniiinfection[19].Ninedifferentphageswithly...</t>
       </text>
     </comment>
-    <comment ref="F37" authorId="0" shapeId="0">
+    <comment ref="F38" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...-SmPesde,u adnodm othnea sreMsIuCltAs SwTeprela tienstearnpdrethteedb raoctchomrdicinrogd itlou ttihoen Eteustro(Mpeearlnin C- om- Diagnostika, Bonn, Germany), or using an E-test (bioMérieux, France) for fosfomycin. mittee on Antimicrobial Susceptibility Testing (EUCAST) breakpoints. The tests were performed, and the results were interpreted according to the European CommitteeonAntimicrobialSusceptibilityTesting(EUCAST)breakpoints. 5.2. Phages,PhageSusceptibility,EfficiencyofPlating(EOP) Twolyticp...</t>
       </text>
     </comment>
-    <comment ref="G37" authorId="0" shapeId="0">
+    <comment ref="G38" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...-SmPesde,u adnodm othnea sreMsIuCltAs SwTeprela tienstearnpdrethteedb raoctchomrdicinrogd itlou ttihoen Eteustro(Mpeearlnin C- om- Diagnostika, Bonn, Germany), or using an E-test (bioMérieux, France) for fosfomycin. mittee on Antimicrobial Susceptibility Testing (EUCAST) breakpoints. The tests were performed, and the results were interpreted according to the European CommitteeonAntimicrobialSusceptibilityTesting(EUCAST)breakpoints. 5.2. Phages,PhageSusceptibility,EfficiencyofPlating(EOP) Twolyticp...</t>
       </text>
     </comment>
-    <comment ref="H37" authorId="0" shapeId="0">
+    <comment ref="H38" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...-SmPesde,u adnodm othnea sreMsIuCltAs SwTeprela tienstearnpdrethteedb raoctchomrdicinrogd itlou ttihoen Eteustro(Mpeearlnin C- om- Diagnostika, Bonn, Germany), or using an E-test (bioMérieux, France) for fosfomycin. mittee on Antimicrobial Susceptibility Testing (EUCAST) breakpoints. The tests were performed, and the results were interpreted according to the European CommitteeonAntimicrobialSusceptibilityTesting(EUCAST)breakpoints. 5.2. Phages,PhageSusceptibility,EfficiencyofPlating(EOP) Twolyticp...</t>
       </text>
     </comment>
-    <comment ref="I37" authorId="0" shapeId="0">
+    <comment ref="I38" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...-SmPesde,u adnodm othnea sreMsIuCltAs SwTeprela tienstearnpdrethteedb raoctchomrdicinrogd itlou ttihoen Eteustro(Mpeearlnin C- om- Diagnostika, Bonn, Germany), or using an E-test (bioMérieux, France) for fosfomycin. mittee on Antimicrobial Susceptibility Testing (EUCAST) breakpoints. The tests were performed, and the results were interpreted according to the European CommitteeonAntimicrobialSusceptibilityTesting(EUCAST)breakpoints. 5.2. Phages,PhageSusceptibility,EfficiencyofPlating(EOP) Twolyticp...</t>
       </text>
     </comment>
-    <comment ref="J37" authorId="0" shapeId="0">
+    <comment ref="J38" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...phages.Wereportacaseofa54-year-oldmanwithrelapsing multidrug-resistantP.aeruginosaLVADdrivelineinfection,whowastreatedwithacombinationof Citation:Racenis,K.;Lacis,J.; Rezevska,D.;Mukane,L.;Vilde,A.; twolyticantipseudomonalphagesadministeredintravenouslyandlocally.Treatmentwascombined Putnins,I.;Djebara,S.;Merabishvili, withLVADdrivelinerepositioningandsystemicantibioticadministration,resultinginasuccessful M.;Pirnay,J.-P.;Kalnina,M.;etal. outcomewithclinicalcureanderadicationofthetarget...
@@ -2235,19 +2291,19 @@
 ...portswherephagetherapywasusedforLVAD infectiontreatment,mildnauseawasnotedinacasedescribedbyMulzeretal.[8]. Ina caseofphagetreatmentforan82-year-oldmanpublishedbyAslametal.[9],usinghighin- travenousphageconcentrationsataconcentrationof1011 PFU/mL,thepatientdeveloped fever,wheezing,shortnessofbreath,andsymptomsdisappearedwhenthephageconcen- trationwasdecreasedto1010PFU/mL.InanothercasedescribedbyTkhilaishvilietal.[10], increasedlivermarkerswereobserved,buttheyreturnedtoanormalran...</t>
       </text>
     </comment>
-    <comment ref="K37" authorId="0" shapeId="0">
+    <comment ref="K38" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...-SmPesde,u adnodm othnea sreMsIuCltAs SwTeprela tienstearnpdrethteedb raoctchomrdicinrogd itlou ttihoen Eteustro(Mpeearlnin C- om- Diagnostika, Bonn, Germany), or using an E-test (bioMérieux, France) for fosfomycin. mittee on Antimicrobial Susceptibility Testing (EUCAST) breakpoints. The tests were performed, and the results were interpreted according to the European CommitteeonAntimicrobialSusceptibilityTesting(EUCAST)breakpoints. 5.2. Phages,PhageSusceptibility,EfficiencyofPlating(EOP) Twolyticp...</t>
       </text>
     </comment>
-    <comment ref="L37" authorId="0" shapeId="0">
+    <comment ref="L38" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...-SmPesde,u adnodm othnea sreMsIuCltAs SwTeprela tienstearnpdrethteedb raoctchomrdicinrogd itlou ttihoen Eteustro(Mpeearlnin C- om- Diagnostika, Bonn, Germany), or using an E-test (bioMérieux, France) for fosfomycin. mittee on Antimicrobial Susceptibility Testing (EUCAST) breakpoints. The tests were performed, and the results were interpreted according to the European CommitteeonAntimicrobialSusceptibilityTesting(EUCAST)breakpoints. 5.2. Phages,PhageSusceptibility,EfficiencyofPlating(EOP) Twolyticp...</t>
       </text>
     </comment>
-    <comment ref="F38" authorId="0" shapeId="0">
+    <comment ref="F39" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...nces such as antibiotics. We report here the case of Citation: a patient with a catastrophic relapsing Staphylococcus aureus knee megaprosthesis FerryT,BataillerC,PetitjeanC, infection without prosthesis loosening. We firstly perform phage susceptibility testing ChateauJ,FevreC,ForestierE, BrossetS,LeboucherG,KolendaC, of the patient’s strain to select an active cocktail, under the supervision of the French LaurentFandLustigS (2020)The health authority. Then, we performed, as salvage therapy, a de...
@@ -2255,7 +2311,7 @@
 ...dly kill in vitro specifically the targeted bacteria and self-replicate in an exponential and self- CASE DESCRIPTION sustained reaction (4). They are considered to have a high potential in patients with PJI as it has been demonstrated that A 49-year-old man had a past history of trauma in 2012 with theyhaveasynergisticanti-biofilmactivitywithantibiotics(5).In right scapula fracture, sternoclavicular luxation complicated by afewpatientswithrelapsingchronicPJIforwhomexplantation brachial pl...</t>
       </text>
     </comment>
-    <comment ref="G38" authorId="0" shapeId="0">
+    <comment ref="G39" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...nces such as antibiotics. We report here the case of Citation: a patient with a catastrophic relapsing Staphylococcus aureus knee megaprosthesis FerryT,BataillerC,PetitjeanC, infection without prosthesis loosening. We firstly perform phage susceptibility testing ChateauJ,FevreC,ForestierE, BrossetS,LeboucherG,KolendaC, of the patient’s strain to select an active cocktail, under the supervision of the French LaurentFandLustigS (2020)The health authority. Then, we performed, as salvage therapy, a de...
@@ -2263,7 +2319,7 @@
 ...dly kill in vitro specifically the targeted bacteria and self-replicate in an exponential and self- CASE DESCRIPTION sustained reaction (4). They are considered to have a high potential in patients with PJI as it has been demonstrated that A 49-year-old man had a past history of trauma in 2012 with theyhaveasynergisticanti-biofilmactivitywithantibiotics(5).In right scapula fracture, sternoclavicular luxation complicated by afewpatientswithrelapsingchronicPJIforwhomexplantation brachial pl...</t>
       </text>
     </comment>
-    <comment ref="H38" authorId="0" shapeId="0">
+    <comment ref="H39" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...nces such as antibiotics. We report here the case of Citation: a patient with a catastrophic relapsing Staphylococcus aureus knee megaprosthesis FerryT,BataillerC,PetitjeanC, infection without prosthesis loosening. We firstly perform phage susceptibility testing ChateauJ,FevreC,ForestierE, BrossetS,LeboucherG,KolendaC, of the patient’s strain to select an active cocktail, under the supervision of the French LaurentFandLustigS (2020)The health authority. Then, we performed, as salvage therapy, a de...
@@ -2271,7 +2327,7 @@
 ...dly kill in vitro specifically the targeted bacteria and self-replicate in an exponential and self- CASE DESCRIPTION sustained reaction (4). They are considered to have a high potential in patients with PJI as it has been demonstrated that A 49-year-old man had a past history of trauma in 2012 with theyhaveasynergisticanti-biofilmactivitywithantibiotics(5).In right scapula fracture, sternoclavicular luxation complicated by afewpatientswithrelapsingchronicPJIforwhomexplantation brachial pl...</t>
       </text>
     </comment>
-    <comment ref="I38" authorId="0" shapeId="0">
+    <comment ref="I39" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...nces such as antibiotics. We report here the case of Citation: a patient with a catastrophic relapsing Staphylococcus aureus knee megaprosthesis FerryT,BataillerC,PetitjeanC, infection without prosthesis loosening. We firstly perform phage susceptibility testing ChateauJ,FevreC,ForestierE, BrossetS,LeboucherG,KolendaC, of the patient’s strain to select an active cocktail, under the supervision of the French LaurentFandLustigS (2020)The health authority. Then, we performed, as salvage therapy, a de...
@@ -2279,7 +2335,7 @@
 ...dly kill in vitro specifically the targeted bacteria and self-replicate in an exponential and self- CASE DESCRIPTION sustained reaction (4). They are considered to have a high potential in patients with PJI as it has been demonstrated that A 49-year-old man had a past history of trauma in 2012 with theyhaveasynergisticanti-biofilmactivitywithantibiotics(5).In right scapula fracture, sternoclavicular luxation complicated by afewpatientswithrelapsingchronicPJIforwhomexplantation brachial pl...</t>
       </text>
     </comment>
-    <comment ref="J38" authorId="0" shapeId="0">
+    <comment ref="J39" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...substances such as antibiotics. We report here the case of Citation: a patient with a catastrophic relapsing Staphylococcus aureus knee megaprosthesis FerryT,BataillerC,PetitjeanC, infection without prosthesis loosening. We firstly perform phage susceptibility testing ChateauJ,FevreC,ForestierE, BrossetS,LeboucherG,KolendaC, of the patient’s strain to select an active cocktail, under the supervision of the French LaurentFandLustigS (2020)The health authority. Then, we performed, as salvage thera...
@@ -2287,7 +2343,7 @@
 ...inical was performed. Unfortunately, in 2016, a purulent discharge situation, the surface of the infected joint is large, and there is appeared. As methicillin-susceptible S. aureus (only resistant no anatomical joint to contain the phages administered during to penicillin) grew in culture from the discharge sample, DAIRsurgery. but also from the puncture of an abscess in close contact The Defensive Antibacterial Coating (DAC(cid:13)R) hydrogel with the prosthesis, clindamycin was prescribed as...</t>
       </text>
     </comment>
-    <comment ref="K38" authorId="0" shapeId="0">
+    <comment ref="K39" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...nces such as antibiotics. We report here the case of Citation: a patient with a catastrophic relapsing Staphylococcus aureus knee megaprosthesis FerryT,BataillerC,PetitjeanC, infection without prosthesis loosening. We firstly perform phage susceptibility testing ChateauJ,FevreC,ForestierE, BrossetS,LeboucherG,KolendaC, of the patient’s strain to select an active cocktail, under the supervision of the French LaurentFandLustigS (2020)The health authority. Then, we performed, as salvage therapy, a de...
@@ -2295,7 +2351,7 @@
 ...dly kill in vitro specifically the targeted bacteria and self-replicate in an exponential and self- CASE DESCRIPTION sustained reaction (4). They are considered to have a high potential in patients with PJI as it has been demonstrated that A 49-year-old man had a past history of trauma in 2012 with theyhaveasynergisticanti-biofilmactivitywithantibiotics(5).In right scapula fracture, sternoclavicular luxation complicated by afewpatientswithrelapsingchronicPJIforwhomexplantation brachial pl...</t>
       </text>
     </comment>
-    <comment ref="L38" authorId="0" shapeId="0">
+    <comment ref="L39" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...nces such as antibiotics. We report here the case of Citation: a patient with a catastrophic relapsing Staphylococcus aureus knee megaprosthesis FerryT,BataillerC,PetitjeanC, infection without prosthesis loosening. We firstly perform phage susceptibility testing ChateauJ,FevreC,ForestierE, BrossetS,LeboucherG,KolendaC, of the patient’s strain to select an active cocktail, under the supervision of the French LaurentFandLustigS (2020)The health authority. Then, we performed, as salvage therapy, a de...
@@ -2303,35 +2359,35 @@
 ...dly kill in vitro specifically the targeted bacteria and self-replicate in an exponential and self- CASE DESCRIPTION sustained reaction (4). They are considered to have a high potential in patients with PJI as it has been demonstrated that A 49-year-old man had a past history of trauma in 2012 with theyhaveasynergisticanti-biofilmactivitywithantibiotics(5).In right scapula fracture, sternoclavicular luxation complicated by afewpatientswithrelapsingchronicPJIforwhomexplantation brachial pl...</t>
       </text>
     </comment>
-    <comment ref="F39" authorId="0" shapeId="0">
+    <comment ref="F40" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...roup, Darien, CT, USA dDivision of Vascular Surgery and Endovascular Therapy, Department of Surgery, Yale University School of Medicine, 330 Cedar Str., Boardman 204, New Haven, CT 06510, USA A R T I C L E I N F O A B S T R A C T Keywords: A 48-year-old woman presented with an acute type B aortic dissection. Despite medical management with anti- Mycotic aneurysm impulse therapy in intensive care, she continued to have chest and back pain and underwent aortic arch Ruptured aneurysm debranc...
 ...pain, and CTA demonstrated aortic arch contrast extravasation just Case description proximal to the endograft (Fig. 1). Cardiac surgery deemed open repair to be prohibitive risk given prior operations, therefore endovascular The patient is a 48-year-old woman with medical history of coronary repair approach was chosen for this patient. The debranching grafts artery disease, congestive heart failure, diabetes, and hypertension. In were identified by previously placed radio-opaque markers,...</t>
       </text>
     </comment>
-    <comment ref="G39" authorId="0" shapeId="0">
+    <comment ref="G40" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...roup, Darien, CT, USA dDivision of Vascular Surgery and Endovascular Therapy, Department of Surgery, Yale University School of Medicine, 330 Cedar Str., Boardman 204, New Haven, CT 06510, USA A R T I C L E I N F O A B S T R A C T Keywords: A 48-year-old woman presented with an acute type B aortic dissection. Despite medical management with anti- Mycotic aneurysm impulse therapy in intensive care, she continued to have chest and back pain and underwent aortic arch Ruptured aneurysm debranc...
 ...pain, and CTA demonstrated aortic arch contrast extravasation just Case description proximal to the endograft (Fig. 1). Cardiac surgery deemed open repair to be prohibitive risk given prior operations, therefore endovascular The patient is a 48-year-old woman with medical history of coronary repair approach was chosen for this patient. The debranching grafts artery disease, congestive heart failure, diabetes, and hypertension. In were identified by previously placed radio-opaque markers,...</t>
       </text>
     </comment>
-    <comment ref="H39" authorId="0" shapeId="0">
+    <comment ref="H40" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...roup, Darien, CT, USA dDivision of Vascular Surgery and Endovascular Therapy, Department of Surgery, Yale University School of Medicine, 330 Cedar Str., Boardman 204, New Haven, CT 06510, USA A R T I C L E I N F O A B S T R A C T Keywords: A 48-year-old woman presented with an acute type B aortic dissection. Despite medical management with anti- Mycotic aneurysm impulse therapy in intensive care, she continued to have chest and back pain and underwent aortic arch Ruptured aneurysm debranc...
 ...pain, and CTA demonstrated aortic arch contrast extravasation just Case description proximal to the endograft (Fig. 1). Cardiac surgery deemed open repair to be prohibitive risk given prior operations, therefore endovascular The patient is a 48-year-old woman with medical history of coronary repair approach was chosen for this patient. The debranching grafts artery disease, congestive heart failure, diabetes, and hypertension. In were identified by previously placed radio-opaque markers,...</t>
       </text>
     </comment>
-    <comment ref="I39" authorId="0" shapeId="0">
+    <comment ref="I40" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...roup, Darien, CT, USA dDivision of Vascular Surgery and Endovascular Therapy, Department of Surgery, Yale University School of Medicine, 330 Cedar Str., Boardman 204, New Haven, CT 06510, USA A R T I C L E I N F O A B S T R A C T Keywords: A 48-year-old woman presented with an acute type B aortic dissection. Despite medical management with anti- Mycotic aneurysm impulse therapy in intensive care, she continued to have chest and back pain and underwent aortic arch Ruptured aneurysm debranc...
 ...pain, and CTA demonstrated aortic arch contrast extravasation just Case description proximal to the endograft (Fig. 1). Cardiac surgery deemed open repair to be prohibitive risk given prior operations, therefore endovascular The patient is a 48-year-old woman with medical history of coronary repair approach was chosen for this patient. The debranching grafts artery disease, congestive heart failure, diabetes, and hypertension. In were identified by previously placed radio-opaque markers,...</t>
       </text>
     </comment>
-    <comment ref="J39" authorId="0" shapeId="0">
+    <comment ref="J40" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...The management of MTAA is challenging, and ruptured MTAA even biotic treatment and underwent FDA-approved phage therapy. Five more so. Mortality rates for thoracic aortic graft infections range be- daily treatments with the combination of intravenous (1 ×109 phage tween 25 % and 75 %(7) with at least 20 % risk of re-infection with open was diluted into 100 mL of sterile normal saline) and local therapy surgical repair.8 The complete resection of the infected aorta and graft, administer...
@@ -2339,45 +2395,45 @@
 ...is an alternative treatment for patients who Patient tolerated all treatments well without adverse reactions. In cannot tolerate open repair.7 Current literature consists of case reports addition to phage therapy, patient was treated with intravenous erta- and small series (Table 1). Frankel and colleagues reviewed their penem 1000 mg daily for 6 months. Following ertapenem therapy, pa- 30-year experience in a study of 75 mycotic aortic aneurysms.10 The tient was transitioned to oral o...</t>
       </text>
     </comment>
-    <comment ref="K39" authorId="0" shapeId="0">
+    <comment ref="K40" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...roup, Darien, CT, USA dDivision of Vascular Surgery and Endovascular Therapy, Department of Surgery, Yale University School of Medicine, 330 Cedar Str., Boardman 204, New Haven, CT 06510, USA A R T I C L E I N F O A B S T R A C T Keywords: A 48-year-old woman presented with an acute type B aortic dissection. Despite medical management with anti- Mycotic aneurysm impulse therapy in intensive care, she continued to have chest and back pain and underwent aortic arch Ruptured aneurysm debranc...
 ...pain, and CTA demonstrated aortic arch contrast extravasation just Case description proximal to the endograft (Fig. 1). Cardiac surgery deemed open repair to be prohibitive risk given prior operations, therefore endovascular The patient is a 48-year-old woman with medical history of coronary repair approach was chosen for this patient. The debranching grafts artery disease, congestive heart failure, diabetes, and hypertension. In were identified by previously placed radio-opaque markers,...</t>
       </text>
     </comment>
-    <comment ref="L39" authorId="0" shapeId="0">
+    <comment ref="L40" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...roup, Darien, CT, USA dDivision of Vascular Surgery and Endovascular Therapy, Department of Surgery, Yale University School of Medicine, 330 Cedar Str., Boardman 204, New Haven, CT 06510, USA A R T I C L E I N F O A B S T R A C T Keywords: A 48-year-old woman presented with an acute type B aortic dissection. Despite medical management with anti- Mycotic aneurysm impulse therapy in intensive care, she continued to have chest and back pain and underwent aortic arch Ruptured aneurysm debranc...
 ...pain, and CTA demonstrated aortic arch contrast extravasation just Case description proximal to the endograft (Fig. 1). Cardiac surgery deemed open repair to be prohibitive risk given prior operations, therefore endovascular The patient is a 48-year-old woman with medical history of coronary repair approach was chosen for this patient. The debranching grafts artery disease, congestive heart failure, diabetes, and hypertension. In were identified by previously placed radio-opaque markers,...</t>
       </text>
     </comment>
-    <comment ref="F40" authorId="0" shapeId="0">
+    <comment ref="F41" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...luatedbytheWestergrenmethod usinganSRS/100II(GreinerBio-One,Kremsmünster,Austria)automaticanalyzer. • Patientfollow-upforPJIrelapse: thetreatmentoutcomeofPJIwasfollowedupfor 12monthsaftersurgery,andthedischargeofpatientsfromthehospitalusingphysical examinationsandphoneinterviewsrecordedasin-personandremoteconsultations. Duringsurveyingpatients,theirdiseasehistorywascollected,withfocusbeingplaced onpainintheoperatedhipjoint,temperaturerises,edema,hyperemiaofthepost- operativescaroroperatedhip,pos...</t>
       </text>
     </comment>
-    <comment ref="G40" authorId="0" shapeId="0">
+    <comment ref="G41" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...luatedbytheWestergrenmethod usinganSRS/100II(GreinerBio-One,Kremsmünster,Austria)automaticanalyzer. • Patientfollow-upforPJIrelapse: thetreatmentoutcomeofPJIwasfollowedupfor 12monthsaftersurgery,andthedischargeofpatientsfromthehospitalusingphysical examinationsandphoneinterviewsrecordedasin-personandremoteconsultations. Duringsurveyingpatients,theirdiseasehistorywascollected,withfocusbeingplaced onpainintheoperatedhipjoint,temperaturerises,edema,hyperemiaofthepost- operativescaroroperatedhip,pos...</t>
       </text>
     </comment>
-    <comment ref="H40" authorId="0" shapeId="0">
+    <comment ref="H41" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...luatedbytheWestergrenmethod usinganSRS/100II(GreinerBio-One,Kremsmünster,Austria)automaticanalyzer. • Patientfollow-upforPJIrelapse: thetreatmentoutcomeofPJIwasfollowedupfor 12monthsaftersurgery,andthedischargeofpatientsfromthehospitalusingphysical examinationsandphoneinterviewsrecordedasin-personandremoteconsultations. Duringsurveyingpatients,theirdiseasehistorywascollected,withfocusbeingplaced onpainintheoperatedhipjoint,temperaturerises,edema,hyperemiaofthepost- operativescaroroperatedhip,pos...</t>
       </text>
     </comment>
-    <comment ref="I40" authorId="0" shapeId="0">
+    <comment ref="I41" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...luatedbytheWestergrenmethod usinganSRS/100II(GreinerBio-One,Kremsmünster,Austria)automaticanalyzer. • Patientfollow-upforPJIrelapse: thetreatmentoutcomeofPJIwasfollowedupfor 12monthsaftersurgery,andthedischargeofpatientsfromthehospitalusingphysical examinationsandphoneinterviewsrecordedasin-personandremoteconsultations. Duringsurveyingpatients,theirdiseasehistorywascollected,withfocusbeingplaced onpainintheoperatedhipjoint,temperaturerises,edema,hyperemiaofthepost- operativescaroroperatedhip,pos...</t>
       </text>
     </comment>
-    <comment ref="J40" authorId="0" shapeId="0">
+    <comment ref="J41" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...eryintheform ofaone-stagetreatmentofdeepPJIaccordingtotheclinicalguidelinesof2013[38] and2016[39],includingetiotropicantibiotictherapyforupto12weeks. (6) Invitrodeterminedsusceptibilityoftheisolatedstaphylococcusbacteriatoastaphy- lococcal phage preparation with a titer of at least 104 plaque forming units/mL (PFU/mL). (7) Eligibilityofthepatientforthephagetherapyprotocolwithinthefirsttendaysafter revisionsurgery. Thecriteriaforexcludingpatientsfromthestudywereasfollows: (1) Patientsunderthea...
@@ -2385,62 +2441,62 @@
 ...y. Thecriteriaforearlywithdrawalofpatientsfromthestudy: (1) Life-threateningconditionsrequiringurgentsurgerywithin12±2daysaftercom- pletedrevisionarthroplasty; (2) Lack of sensitivity of isolated staphylococcus bacteria to a staphylococcal phage preparation,definedasabacteriophagetiterlessthan104 PFU/mL,aftercompleted revisionarthroplasty. 2.3. SurgicalTreatmentandAntibioticTherapyProtocols SurgicaltreatmentofPJIinpatientsofbothgroupswasperformedinonestage,with implantationofacementedendopros...</t>
       </text>
     </comment>
-    <comment ref="K40" authorId="0" shapeId="0">
+    <comment ref="K41" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...luatedbytheWestergrenmethod usinganSRS/100II(GreinerBio-One,Kremsmünster,Austria)automaticanalyzer. • Patientfollow-upforPJIrelapse: thetreatmentoutcomeofPJIwasfollowedupfor 12monthsaftersurgery,andthedischargeofpatientsfromthehospitalusingphysical examinationsandphoneinterviewsrecordedasin-personandremoteconsultations. Duringsurveyingpatients,theirdiseasehistorywascollected,withfocusbeingplaced onpainintheoperatedhipjoint,temperaturerises,edema,hyperemiaofthepost- operativescaroroperatedhip,pos...</t>
       </text>
     </comment>
-    <comment ref="L40" authorId="0" shapeId="0">
+    <comment ref="L41" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...luatedbytheWestergrenmethod usinganSRS/100II(GreinerBio-One,Kremsmünster,Austria)automaticanalyzer. • Patientfollow-upforPJIrelapse: thetreatmentoutcomeofPJIwasfollowedupfor 12monthsaftersurgery,andthedischargeofpatientsfromthehospitalusingphysical examinationsandphoneinterviewsrecordedasin-personandremoteconsultations. Duringsurveyingpatients,theirdiseasehistorywascollected,withfocusbeingplaced onpainintheoperatedhipjoint,temperaturerises,edema,hyperemiaofthepost- operativescaroroperatedhip,pos...</t>
       </text>
     </comment>
-    <comment ref="F41" authorId="0" shapeId="0">
+    <comment ref="F42" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...G RAND ROUNDS Severe Darier disease complicated by recurrent multidrug-resistant cutaneous infection Ivana Ho, MD,a Elizabeth W. Beiermann, MD,a Alecia R. Anyim, MBBS, MD,a Jack B. Newcomer, MD,b and Marian T. McEvoy, MDb CASE DESCRIPTION A 39-year-old woman with severe Darier disease (DD) and a history of multiple hospitalizations for recurrent multidrug resistant cutaneous infections presented with painful, worsening lesions involving the gluteal and perineal regions. Acitretin was dis...</t>
       </text>
     </comment>
-    <comment ref="G41" authorId="0" shapeId="0">
+    <comment ref="G42" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...G RAND ROUNDS Severe Darier disease complicated by recurrent multidrug-resistant cutaneous infection Ivana Ho, MD,a Elizabeth W. Beiermann, MD,a Alecia R. Anyim, MBBS, MD,a Jack B. Newcomer, MD,b and Marian T. McEvoy, MDb CASE DESCRIPTION A 39-year-old woman with severe Darier disease (DD) and a history of multiple hospitalizations for recurrent multidrug resistant cutaneous infections presented with painful, worsening lesions involving the gluteal and perineal regions. Acitretin was dis...</t>
       </text>
     </comment>
-    <comment ref="H41" authorId="0" shapeId="0">
+    <comment ref="H42" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...G RAND ROUNDS Severe Darier disease complicated by recurrent multidrug-resistant cutaneous infection Ivana Ho, MD,a Elizabeth W. Beiermann, MD,a Alecia R. Anyim, MBBS, MD,a Jack B. Newcomer, MD,b and Marian T. McEvoy, MDb CASE DESCRIPTION A 39-year-old woman with severe Darier disease (DD) and a history of multiple hospitalizations for recurrent multidrug resistant cutaneous infections presented with painful, worsening lesions involving the gluteal and perineal regions. Acitretin was dis...</t>
       </text>
     </comment>
-    <comment ref="I41" authorId="0" shapeId="0">
+    <comment ref="I42" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...G RAND ROUNDS Severe Darier disease complicated by recurrent multidrug-resistant cutaneous infection Ivana Ho, MD,a Elizabeth W. Beiermann, MD,a Alecia R. Anyim, MBBS, MD,a Jack B. Newcomer, MD,b and Marian T. McEvoy, MDb CASE DESCRIPTION A 39-year-old woman with severe Darier disease (DD) and a history of multiple hospitalizations for recurrent multidrug resistant cutaneous infections presented with painful, worsening lesions involving the gluteal and perineal regions. Acitretin was dis...</t>
       </text>
     </comment>
-    <comment ref="J41" authorId="0" shapeId="0">
+    <comment ref="J42" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...1, B). Wound cultures grew polymicrobial organisms, including carbapenem-resistant Pseudomonas aeruginosa, methicillin-resistant Staphylococcus aureus, Enterococcus faecalis, and Proteus mirabilis. The abscess was drained and treated with intravenous antibiotics. Dermatologic therapy included reinitiation of acitretin, keratolytics, and antiseptic soaks. Due to persistent infection with progressively resistant organisms despite culture-directed antimicrobial therapy, adjunctive investi...
 ...fist-line treatment.1 Patients with DD also frequently exhibit cutaneous dysbiosis with increased colonization of organisms, such as S. aureus, which is also correlated with increased disease severity.4 Although antimicrobial therapies and topical antiseptics may temporarily reduce microbial burden, they do not correct the underlying epidermal barrier defect that drives recurrent infection and may contribute to antimicrobial resistance.5 Our patient ultimately required adjunctive in...</t>
       </text>
     </comment>
-    <comment ref="K41" authorId="0" shapeId="0">
+    <comment ref="K42" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...G RAND ROUNDS Severe Darier disease complicated by recurrent multidrug-resistant cutaneous infection Ivana Ho, MD,a Elizabeth W. Beiermann, MD,a Alecia R. Anyim, MBBS, MD,a Jack B. Newcomer, MD,b and Marian T. McEvoy, MDb CASE DESCRIPTION A 39-year-old woman with severe Darier disease (DD) and a history of multiple hospitalizations for recurrent multidrug resistant cutaneous infections presented with painful, worsening lesions involving the gluteal and perineal regions. Acitretin was dis...</t>
       </text>
     </comment>
-    <comment ref="L41" authorId="0" shapeId="0">
+    <comment ref="L42" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...G RAND ROUNDS Severe Darier disease complicated by recurrent multidrug-resistant cutaneous infection Ivana Ho, MD,a Elizabeth W. Beiermann, MD,a Alecia R. Anyim, MBBS, MD,a Jack B. Newcomer, MD,b and Marian T. McEvoy, MDb CASE DESCRIPTION A 39-year-old woman with severe Darier disease (DD) and a history of multiple hospitalizations for recurrent multidrug resistant cutaneous infections presented with painful, worsening lesions involving the gluteal and perineal regions. Acitretin was dis...</t>
       </text>
     </comment>
-    <comment ref="J42" authorId="0" shapeId="0">
+    <comment ref="J43" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...ccus aureus, were applied locally. The bacteriophage the thoracotomy scar site with involvement of the pump. solution (10ml) was a 1:1 mixture of PYO bacteriophage with Surgical debridement and vacuum-assisted closure (VAC) ther- (cid:2)106plaque-formingunits/ml(Georgianpharmaceuticalproduct apy were initiated. Intraoperative culture samples tested posi- registration number: R-022600) and Staphylococcal bacterio- tive for methicillin-susceptible Staphylococcus aureus. Intra phage Sb-1 with...
@@ -3996,7 +4052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P42"/>
+  <dimension ref="A1:P43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4990,7 +5046,7 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>EST-053</t>
+          <t>EST-051</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -5000,12 +5056,12 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Phage-Antibiotic Combination Therapy against Recurrent Pseudomonas Septicaemia in a Patient with an Arterial Stent.</t>
+          <t>Case report: Local bacteriophage therapy for fracture-related infection with polymicrobial multi-resistant bacteria: hydrogel application and postoperative phage analysis through metagenomic sequencing</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>Antibiotics (Basel, Switzerland)</t>
+          <t>Frontiers in Medicine</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
@@ -5028,7 +5084,7 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>EST-057</t>
+          <t>EST-053</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -5038,17 +5094,17 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Phage Therapy as a Rescue Treatment for Recurrent Pseudomonas aeruginosa Bentall Infection.</t>
+          <t>Phage-Antibiotic Combination Therapy against Recurrent Pseudomonas Septicaemia in a Patient with an Arterial Stent.</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>Viruses</t>
+          <t>Antibiotics (Basel, Switzerland)</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F28" s="8" t="n"/>
@@ -5066,7 +5122,7 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>EST-058</t>
+          <t>EST-057</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -5076,12 +5132,12 @@
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Resolution of acute rejection in a bilateral double-lung transplanted cystic fibrosis patient following phage intervention.</t>
+          <t>Phage Therapy as a Rescue Treatment for Recurrent Pseudomonas aeruginosa Bentall Infection.</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>ASM case reports</t>
+          <t>Viruses</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -5104,7 +5160,7 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>EST-062</t>
+          <t>EST-058</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -5114,17 +5170,17 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Bacteriophage-antibiotic combination therapy against extensively drug-resistant Pseudomonas aeruginosa infection to allow liver transplantation in a toddler.</t>
+          <t>Resolution of acute rejection in a bilateral double-lung transplanted cystic fibrosis patient following phage intervention.</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nature Communications </t>
+          <t>ASM case reports</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F30" s="8" t="n"/>
@@ -5142,7 +5198,7 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>EST-085</t>
+          <t>EST-062</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -5152,17 +5208,17 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>First-in-human application of double-stranded RNA bacteriophage in the treatment of pulmonary Pseudomonas aeruginosa infection.</t>
+          <t>Bacteriophage-antibiotic combination therapy against extensively drug-resistant Pseudomonas aeruginosa infection to allow liver transplantation in a toddler.</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Microbial biotechnology</t>
+          <t xml:space="preserve">Nature Communications </t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F31" s="8" t="n"/>
@@ -5180,7 +5236,7 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>EST-088</t>
+          <t>EST-085</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -5190,17 +5246,17 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Case report: Personalized triple phage-antibiotic combination therapy to rescue necrotizing fasciitis caused by Panton-Valentine leukocidin-producing MRSA in a 12-year-old boy.</t>
+          <t>First-in-human application of double-stranded RNA bacteriophage in the treatment of pulmonary Pseudomonas aeruginosa infection.</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>Frontiers in cellular and infection microbiology</t>
+          <t>Microbial biotechnology</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F32" s="8" t="n"/>
@@ -5218,7 +5274,7 @@
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>EST-094</t>
+          <t>EST-088</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -5228,17 +5284,17 @@
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Timely bespoke phage-antibiotic combination to treat refractory Pseudomonas aeruginosa mediastinitis and vascular graft infection.</t>
+          <t>Case report: Personalized triple phage-antibiotic combination therapy to rescue necrotizing fasciitis caused by Panton-Valentine leukocidin-producing MRSA in a 12-year-old boy.</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nature Communications </t>
+          <t>Frontiers in cellular and infection microbiology</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F33" s="8" t="n"/>
@@ -5256,7 +5312,7 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>EST-095</t>
+          <t>EST-094</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
@@ -5266,17 +5322,17 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Bacterial lysis, autophagy and innate immune responses during adjunctive phage therapy in a child.</t>
+          <t>Timely bespoke phage-antibiotic combination to treat refractory Pseudomonas aeruginosa mediastinitis and vascular graft infection.</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>EMBO molecular medicine</t>
+          <t xml:space="preserve">Nature Communications </t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="F34" s="8" t="n"/>
@@ -5294,7 +5350,7 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>EST-105</t>
+          <t>EST-095</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -5304,17 +5360,17 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Innovations for the treatment of a complex bone and joint infection due to XDR Pseudomonas aeruginosa including local application of a selected cocktail of bacteriophages.</t>
+          <t>Bacterial lysis, autophagy and innate immune responses during adjunctive phage therapy in a child.</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>The Journal of antimicrobial chemotherapy</t>
+          <t>EMBO molecular medicine</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F35" s="8" t="n"/>
@@ -5332,7 +5388,7 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>EST-106</t>
+          <t>EST-105</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
@@ -5342,12 +5398,12 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Phage treatment of an aortic graft infected with Pseudomonas aeruginosa.</t>
+          <t>Innovations for the treatment of a complex bone and joint infection due to XDR Pseudomonas aeruginosa including local application of a selected cocktail of bacteriophages.</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>Evolution, medicine, and public health</t>
+          <t>The Journal of antimicrobial chemotherapy</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -5370,7 +5426,7 @@
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>EST-124</t>
+          <t>EST-106</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -5380,17 +5436,17 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>Successful Bacteriophage-Antibiotic Combination Therapy against Multidrug-Resistant Pseudomonas aeruginosa Left Ventricular Assist Device Driveline Infection.</t>
+          <t>Phage treatment of an aortic graft infected with Pseudomonas aeruginosa.</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Viruses</t>
+          <t>Evolution, medicine, and public health</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F37" s="8" t="n"/>
@@ -5408,7 +5464,7 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>EST-135</t>
+          <t>EST-124</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
@@ -5418,17 +5474,17 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>The Potential Innovative Use of Bacteriophages Within the DAC® Hydrogel to Treat Patients With Knee Megaprosthesis Infection Requiring “Debridement Antibiotics and Implant Retention” and Soft Tissue Coverage as Salvage Therapy</t>
+          <t>Successful Bacteriophage-Antibiotic Combination Therapy against Multidrug-Resistant Pseudomonas aeruginosa Left Ventricular Assist Device Driveline Infection.</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>Frontiers in Medicine</t>
+          <t>Viruses</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F38" s="8" t="n"/>
@@ -5446,7 +5502,7 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>EST-170</t>
+          <t>EST-135</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
@@ -5456,17 +5512,17 @@
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Thoracic endovascular aneurysm repair of a ruptured zone 0 mycotic thoracic aortic aneurysm</t>
+          <t>The Potential Innovative Use of Bacteriophages Within the DAC® Hydrogel to Treat Patients With Knee Megaprosthesis Infection Requiring “Debridement Antibiotics and Implant Retention” and Soft Tissue Coverage as Salvage Therapy</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Annals of Vascular Surgery - Brief Reports and Innovations</t>
+          <t>Frontiers in Medicine</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F39" s="8" t="n"/>
@@ -5484,7 +5540,7 @@
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>EST-181</t>
+          <t>EST-170</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
@@ -5494,17 +5550,17 @@
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Short-Term Outcomes of Phage-Antibiotic Combination Treatment in Adult Patients with Periprosthetic Hip Joint Infection.</t>
+          <t>Thoracic endovascular aneurysm repair of a ruptured zone 0 mycotic thoracic aortic aneurysm</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>Viruses</t>
+          <t>Annals of Vascular Surgery - Brief Reports and Innovations</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F40" s="8" t="n"/>
@@ -5522,7 +5578,7 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>EST-184</t>
+          <t>EST-181</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
@@ -5532,17 +5588,17 @@
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Severe Darier disease complicated by recurrent multidrug-resistant cutaneous infection</t>
+          <t>Short-Term Outcomes of Phage-Antibiotic Combination Treatment in Adult Patients with Periprosthetic Hip Joint Infection.</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>JAAD Case Reports</t>
+          <t>Viruses</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F41" s="8" t="n"/>
@@ -5560,7 +5616,7 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>EST-208</t>
+          <t>EST-184</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
@@ -5570,17 +5626,17 @@
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Treatment of chronic left ventricular assist device infection with local application of bacteriophages.</t>
+          <t>Severe Darier disease complicated by recurrent multidrug-resistant cutaneous infection</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>European journal of cardio-thoracic surgery : official journal of the European Association for Cardio-thoracic Surgery</t>
+          <t>JAAD Case Reports</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="F42" s="8" t="n"/>
@@ -5595,12 +5651,50 @@
       <c r="O42" s="8" t="n"/>
       <c r="P42" s="8" t="n"/>
     </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>EST-208</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>case report</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>Treatment of chronic left ventricular assist device infection with local application of bacteriophages.</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>European journal of cardio-thoracic surgery : official journal of the European Association for Cardio-thoracic Surgery</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="n"/>
+      <c r="G43" s="8" t="n"/>
+      <c r="H43" s="8" t="n"/>
+      <c r="I43" s="8" t="n"/>
+      <c r="J43" s="8" t="n"/>
+      <c r="K43" s="8" t="n"/>
+      <c r="L43" s="8" t="n"/>
+      <c r="M43" s="8" t="n"/>
+      <c r="N43" s="8" t="n"/>
+      <c r="O43" s="8" t="n"/>
+      <c r="P43" s="8" t="n"/>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="N4 N5 N6 N7 N8 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19 N20 N21 N22 N23 N24 N25 N26 N27 N28 N29 N30 N31 N32 N33 N34 N35 N36 N37 N38 N39 N40 N41 N42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N4 N5 N6 N7 N8 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19 N20 N21 N22 N23 N24 N25 N26 N27 N28 N29 N30 N31 N32 N33 N34 N35 N36 N37 N38 N39 N40 N41 N42 N43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Incluir,Excluir,Buscar más información"</formula1>
     </dataValidation>
-    <dataValidation sqref="F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 G4 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G35 G36 G37 G38 G39 G40 G41 G42 H4 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H35 H36 H37 H38 H39 H40 H41 H42 I4 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 I34 I35 I36 I37 I38 I39 I40 I41 I42 J4 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J35 J36 J37 J38 J39 J40 J41 J42 K4 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 K28 K29 K30 K31 K32 K33 K34 K35 K36 K37 K38 K39 K40 K41 K42 L4 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L35 L36 L37 L38 L39 L40 L41 L42 M4 M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 M28 M29 M30 M31 M32 M33 M34 M35 M36 M37 M38 M39 M40 M41 M42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 G4 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G35 G36 G37 G38 G39 G40 G41 G42 G43 H4 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H35 H36 H37 H38 H39 H40 H41 H42 H43 I4 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 I34 I35 I36 I37 I38 I39 I40 I41 I42 I43 J4 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J35 J36 J37 J38 J39 J40 J41 J42 J43 K4 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 K28 K29 K30 K31 K32 K33 K34 K35 K36 K37 K38 K39 K40 K41 K42 K43 L4 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L35 L36 L37 L38 L39 L40 L41 L42 L43 M4 M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 M28 M29 M30 M31 M32 M33 M34 M35 M36 M37 M38 M39 M40 M41 M42 M43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Sí,No,No está claro,No aplicable"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7234,7 +7328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -7288,7 +7382,7 @@
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>EST-051</t>
+          <t>EST-121</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
@@ -7298,42 +7392,15 @@
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Case report: Local bacteriophage therapy for fracture-related infection with polymicrobial multi-resistant bacteria: hydrogel application and postoperative phage analysis through metagenomic sequencing</t>
+          <t>Do Anti-Phage Antibodies Persist after Phage Therapy? A Preliminary Report</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Frontiers in Medicine</t>
+          <t>Antibiotics</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>EST-121</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>(no clasificable)</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>Do Anti-Phage Antibodies Persist after Phage Therapy? A Preliminary Report</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
-          <t>Antibiotics</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>2022</t>
         </is>

--- a/revision_sistematica/riesgo_sesgo/riesgo_sesgo_nataly_trelles.xlsx
+++ b/revision_sistematica/riesgo_sesgo/riesgo_sesgo_nataly_trelles.xlsx
@@ -13,7 +13,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JBI reporte de caso" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JBI serie de casos" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="No evaluables" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diseño pendiente" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2802,73 +2801,73 @@
 ...at the burden of age-related immune dysregulation in these pa- tientsmaybedisproportionatelycarriedbythemononuclearsystem,whilegranulocyte transcriptionalplasticityremainsrelativelydistinct. Theobservedheterogeneityshouldnotbeinterpretedasaconfoundingfactor,but ratherasacentralcharacteristicsuggestingthattheimmuneresponsetophagesismodu- latedbypatient-specificimmunologicalcontextsratherthanauniversalmechanism. This alignswithmethodologicalinsightsfromothercomplexchronicdiseases. Recenta...</t>
       </text>
     </comment>
-    <comment ref="K19" authorId="0" shapeId="0">
+    <comment ref="K20" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...rbothK.pneumoniaeandMSSA.Duetothecomplexityoftheintervention,some metalworkhadtoberetained. Consequently,thepatientcompletedafurther12weeksof antibiotictreatmentwithvancomycinandmeropenemandatdischargethewoundwas closedanddry. 4. CaseThree A 77-year-old patient presented in 2022 with a periprosthetic joint infection of the right knee. The initial implant was performed in 2018 and revised in 2022 for early tibialloosening. Aroundeightweekslater,thepatientwasreadmittedwithamarkedly swollen,...</t>
       </text>
     </comment>
-    <comment ref="L19" authorId="0" shapeId="0">
+    <comment ref="L20" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...rbothK.pneumoniaeandMSSA.Duetothecomplexityoftheintervention,some metalworkhadtoberetained. Consequently,thepatientcompletedafurther12weeksof antibiotictreatmentwithvancomycinandmeropenemandatdischargethewoundwas closedanddry. 4. CaseThree A 77-year-old patient presented in 2022 with a periprosthetic joint infection of the right knee. The initial implant was performed in 2018 and revised in 2022 for early tibialloosening. Aroundeightweekslater,thepatientwasreadmittedwithamarkedly swollen,...</t>
       </text>
     </comment>
-    <comment ref="N19" authorId="0" shapeId="0">
+    <comment ref="N20" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...rbothK.pneumoniaeandMSSA.Duetothecomplexityoftheintervention,some metalworkhadtoberetained. Consequently,thepatientcompletedafurther12weeksof antibiotictreatmentwithvancomycinandmeropenemandatdischargethewoundwas closedanddry. 4. CaseThree A 77-year-old patient presented in 2022 with a periprosthetic joint infection of the right knee. The initial implant was performed in 2018 and revised in 2022 for early tibialloosening. Aroundeightweekslater,thepatientwasreadmittedwithamarkedly swollen,...</t>
       </text>
     </comment>
-    <comment ref="K21" authorId="0" shapeId="0">
+    <comment ref="K22" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...omtheappliedcocktailswerecapableofpropagatinginsidemostofthesusceptible strains. TheEOPvaluesrangedfrom0.001to0.7. TheisolatedStaphylococcusspp. frompatients1,2,and 3weresusceptibletoBFC1. TheP.aeruginosastrainfromPatient1wasnotavailableforsusceptibility testing. Theextensively drug-resistant (XDR) P.aeruginosa in Patient 2 was non-susceptibleto the phages(i.e.,PNM,14/1)presentinBFC1. GiventhattheS.epidermidisstrainwassusceptibletoBFC1, theMDTdecidedthatitwouldbeinthepatient’sbestinteresttoproceed...</t>
       </text>
     </comment>
-    <comment ref="L21" authorId="0" shapeId="0">
+    <comment ref="L22" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...omtheappliedcocktailswerecapableofpropagatinginsidemostofthesusceptible strains. TheEOPvaluesrangedfrom0.001to0.7. TheisolatedStaphylococcusspp. frompatients1,2,and 3weresusceptibletoBFC1. TheP.aeruginosastrainfromPatient1wasnotavailableforsusceptibility testing. Theextensively drug-resistant (XDR) P.aeruginosa in Patient 2 was non-susceptibleto the phages(i.e.,PNM,14/1)presentinBFC1. GiventhattheS.epidermidisstrainwassusceptibletoBFC1, theMDTdecidedthatitwouldbeinthepatient’sbestinteresttoproceed...</t>
       </text>
     </comment>
-    <comment ref="N21" authorId="0" shapeId="0">
+    <comment ref="N22" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...omtheappliedcocktailswerecapableofpropagatinginsidemostofthesusceptible strains. TheEOPvaluesrangedfrom0.001to0.7. TheisolatedStaphylococcusspp. frompatients1,2,and 3weresusceptibletoBFC1. TheP.aeruginosastrainfromPatient1wasnotavailableforsusceptibility testing. Theextensively drug-resistant (XDR) P.aeruginosa in Patient 2 was non-susceptibleto the phages(i.e.,PNM,14/1)presentinBFC1. GiventhattheS.epidermidisstrainwassusceptibletoBFC1, theMDTdecidedthatitwouldbeinthepatient’sbestinteresttoproceed...</t>
       </text>
     </comment>
-    <comment ref="F22" authorId="0" shapeId="0">
+    <comment ref="F23" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ....ThechangesofantibioticsensitivitywasobservedinisolatesfromM17S:Sensitive;R: Resistant;S-IE:Susceptiblewithincreasedexposure;INS:Insufficientevidence;BT:Bacteriophagetherapy bacteriophage and bacterial host and not due to the bacteriophage confounding role that ETI may have in our findings. Studies have alone; 2) while bacteriophages share similar properties (e.g., capsid demonstratedthat theintroduction ofETIhasbeen showntocause a proteinfolds)(FokineandRossmann,2014),asingle-pointmuta...</t>
       </text>
     </comment>
-    <comment ref="I22" authorId="0" shapeId="0">
+    <comment ref="I23" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ....ThechangesofantibioticsensitivitywasobservedinisolatesfromM17S:Sensitive;R: Resistant;S-IE:Susceptiblewithincreasedexposure;INS:Insufficientevidence;BT:Bacteriophagetherapy bacteriophage and bacterial host and not due to the bacteriophage confounding role that ETI may have in our findings. Studies have alone; 2) while bacteriophages share similar properties (e.g., capsid demonstratedthat theintroduction ofETIhasbeen showntocause a proteinfolds)(FokineandRossmann,2014),asingle-pointmuta...</t>
       </text>
     </comment>
-    <comment ref="J22" authorId="0" shapeId="0">
+    <comment ref="J23" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ....ThechangesofantibioticsensitivitywasobservedinisolatesfromM17S:Sensitive;R: Resistant;S-IE:Susceptiblewithincreasedexposure;INS:Insufficientevidence;BT:Bacteriophagetherapy bacteriophage and bacterial host and not due to the bacteriophage confounding role that ETI may have in our findings. Studies have alone; 2) while bacteriophages share similar properties (e.g., capsid demonstratedthat theintroduction ofETIhasbeen showntocause a proteinfolds)(FokineandRossmann,2014),asingle-pointmuta...</t>
       </text>
     </comment>
-    <comment ref="K22" authorId="0" shapeId="0">
+    <comment ref="K23" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...ty,and Bronchoscopy potentialefficacyofbronchoscopicandnebulisedbacteriophageadministration,offeringinsightsintoapotential Nebulisation breakthroughforthetreatmentofchronicinfectionsparticularlyinchildrenandadolescents. Pseudomonas Method: A 12-year-old female (F12) and a 17-year-old male (M17), both diagnosed with cystic fibrosis and chronic P. aeruginosa lung infection, underwent bacteriophage treatment (BT). The administration involved bronchoscopicinstillationandsubsequentnebulisation...</t>
       </text>
     </comment>
-    <comment ref="L22" authorId="0" shapeId="0">
+    <comment ref="L23" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...ty,and Bronchoscopy potentialefficacyofbronchoscopicandnebulisedbacteriophageadministration,offeringinsightsintoapotential Nebulisation breakthroughforthetreatmentofchronicinfectionsparticularlyinchildrenandadolescents. Pseudomonas Method: A 12-year-old female (F12) and a 17-year-old male (M17), both diagnosed with cystic fibrosis and chronic P. aeruginosa lung infection, underwent bacteriophage treatment (BT). The administration involved bronchoscopicinstillationandsubsequentnebulisation...</t>
       </text>
     </comment>
-    <comment ref="N22" authorId="0" shapeId="0">
+    <comment ref="N23" authorId="0" shapeId="0">
       <text>
         <t>Del artículo:
 ...ty,and Bronchoscopy potentialefficacyofbronchoscopicandnebulisedbacteriophageadministration,offeringinsightsintoapotential Nebulisation breakthroughforthetreatmentofchronicinfectionsparticularlyinchildrenandadolescents. Pseudomonas Method: A 12-year-old female (F12) and a 17-year-old male (M17), both diagnosed with cystic fibrosis and chronic P. aeruginosa lung infection, underwent bacteriophage treatment (BT). The administration involved bronchoscopicinstillationandsubsequentnebulisation...</t>
@@ -5709,7 +5708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R22"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -6441,7 +6440,7 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>EST-129</t>
+          <t>EST-121</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -6451,7 +6450,7 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Phage Therapy for Orthopaedic Infections: The First Three Cases from the United Kingdom</t>
+          <t>Do Anti-Phage Antibodies Persist after Phage Therapy? A Preliminary Report</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -6461,7 +6460,7 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F19" s="8" t="n"/>
@@ -6481,7 +6480,7 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>EST-134</t>
+          <t>EST-129</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -6491,17 +6490,17 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Adapted Bacteriophages for Treating Urinary Tract Infections.</t>
+          <t>Phage Therapy for Orthopaedic Infections: The First Three Cases from the United Kingdom</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>Frontiers in microbiology</t>
+          <t>Antibiotics</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F20" s="8" t="n"/>
@@ -6521,7 +6520,7 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>EST-164</t>
+          <t>EST-134</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -6531,17 +6530,17 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Bacteriophage Application for Difficult-to-treat Musculoskeletal Infections: Development of a Standardized Multidisciplinary Treatment Protocol.</t>
+          <t>Adapted Bacteriophages for Treating Urinary Tract Infections.</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Viruses</t>
+          <t>Frontiers in microbiology</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F21" s="8" t="n"/>
@@ -6561,7 +6560,7 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>EST-169</t>
+          <t>EST-164</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -6571,17 +6570,17 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Safety and tolerability of bronchoscopic and nebulised administration of bacteriophage.</t>
+          <t>Bacteriophage Application for Difficult-to-treat Musculoskeletal Infections: Development of a Standardized Multidisciplinary Treatment Protocol.</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Virus research</t>
+          <t>Viruses</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F22" s="8" t="n"/>
@@ -6598,12 +6597,52 @@
       <c r="Q22" s="8" t="n"/>
       <c r="R22" s="8" t="n"/>
     </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>EST-169</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>case series</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Safety and tolerability of bronchoscopic and nebulised administration of bacteriophage.</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Virus research</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="n"/>
+      <c r="G23" s="8" t="n"/>
+      <c r="H23" s="8" t="n"/>
+      <c r="I23" s="8" t="n"/>
+      <c r="J23" s="8" t="n"/>
+      <c r="K23" s="8" t="n"/>
+      <c r="L23" s="8" t="n"/>
+      <c r="M23" s="8" t="n"/>
+      <c r="N23" s="8" t="n"/>
+      <c r="O23" s="8" t="n"/>
+      <c r="P23" s="8" t="n"/>
+      <c r="Q23" s="8" t="n"/>
+      <c r="R23" s="8" t="n"/>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="P4 P5 P6 P7 P8 P9 P10 P11 P12 P13 P14 P15 P16 P17 P18 P19 P20 P21 P22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P4 P5 P6 P7 P8 P9 P10 P11 P12 P13 P14 P15 P16 P17 P18 P19 P20 P21 P22 P23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Incluir,Excluir,Buscar más información"</formula1>
     </dataValidation>
-    <dataValidation sqref="F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 G4 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 H4 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 I4 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 J4 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 K4 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 L4 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 M4 M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 N4 N5 N6 N7 N8 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19 N20 N21 N22 O4 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 G4 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 H4 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 I4 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 J4 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 K4 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 L4 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 M4 M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 N4 N5 N6 N7 N8 N9 N10 N11 N12 N13 N14 N15 N16 N17 N18 N19 N20 N21 N22 N23 O4 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Sí,No,No está claro,No aplicable"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7320,93 +7359,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Diseño pendiente de decidir: sin diseño no se puede elegir instrumento</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>Estos estudios se leyeron pero su diseño no quedó clasificado. Decidid primero qué son y volved a generar el formulario; forzar un instrumento sobre un diseño que no se sabe da un juicio que no significa nada.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>Nº</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>Diseño</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>Título del artículo</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>Revista</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="inlineStr">
-        <is>
-          <t>Año</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>EST-121</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>(no clasificable)</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>Do Anti-Phage Antibodies Persist after Phage Therapy? A Preliminary Report</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Antibiotics</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>